--- a/research/traditional_assets/database/data/indonesia/indonesia_transportation_railroads.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_transportation_railroads.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0797176745613359</v>
+        <v>0.07957739567730096</v>
       </c>
       <c r="C2">
-        <v>165.6247196956734</v>
+        <v>164.6462675250067</v>
       </c>
       <c r="D2">
-        <v>164.4247196956734</v>
+        <v>165.0682675250068</v>
       </c>
       <c r="E2">
-        <v>-27.1</v>
+        <v>-25.478</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.622</v>
       </c>
       <c r="G2">
         <v>1.2</v>
@@ -1439,28 +1439,28 @@
         <v>23.326</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0815866</v>
       </c>
       <c r="N2">
-        <v>23.326</v>
+        <v>23.2444134</v>
       </c>
       <c r="O2">
-        <v>5.131720000000001</v>
+        <v>5.113770948</v>
       </c>
       <c r="P2">
-        <v>18.19428</v>
+        <v>18.130642452</v>
       </c>
       <c r="Q2">
-        <v>18.36828</v>
+        <v>18.304642452</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0797176745613359</v>
+        <v>0.07998490472454642</v>
       </c>
       <c r="T2">
-        <v>0.4935434922969562</v>
+        <v>0.49743201678172</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>285.9047931890776</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07957739567730096</v>
+        <v>0.07943711679326602</v>
       </c>
       <c r="C3">
-        <v>164.6462675250067</v>
+        <v>163.6728727587283</v>
       </c>
       <c r="D3">
-        <v>165.0682675250068</v>
+        <v>165.7168727587283</v>
       </c>
       <c r="E3">
-        <v>-25.478</v>
+        <v>-23.856</v>
       </c>
       <c r="F3">
-        <v>1.622</v>
+        <v>3.244</v>
       </c>
       <c r="G3">
         <v>1.2</v>
@@ -1521,28 +1521,28 @@
         <v>23.326</v>
       </c>
       <c r="M3">
-        <v>0.0815866</v>
+        <v>0.1631732</v>
       </c>
       <c r="N3">
-        <v>23.2444134</v>
+        <v>23.1628268</v>
       </c>
       <c r="O3">
-        <v>5.113770948</v>
+        <v>5.095821896</v>
       </c>
       <c r="P3">
-        <v>18.130642452</v>
+        <v>18.067004904</v>
       </c>
       <c r="Q3">
-        <v>18.304642452</v>
+        <v>18.241004904</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07998490472454642</v>
+        <v>0.08025758856455717</v>
       </c>
       <c r="T3">
-        <v>0.49743201678172</v>
+        <v>0.5013998989090301</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>285.9047931890776</v>
+        <v>142.9523965945388</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07943711679326602</v>
+        <v>0.07929683790923107</v>
       </c>
       <c r="C4">
-        <v>163.6728727587283</v>
+        <v>162.7045952484197</v>
       </c>
       <c r="D4">
-        <v>165.7168727587283</v>
+        <v>166.3705952484197</v>
       </c>
       <c r="E4">
-        <v>-23.856</v>
+        <v>-22.234</v>
       </c>
       <c r="F4">
-        <v>3.244</v>
+        <v>4.866</v>
       </c>
       <c r="G4">
         <v>1.2</v>
@@ -1603,28 +1603,28 @@
         <v>23.326</v>
       </c>
       <c r="M4">
-        <v>0.1631732</v>
+        <v>0.2447598</v>
       </c>
       <c r="N4">
-        <v>23.1628268</v>
+        <v>23.0812402</v>
       </c>
       <c r="O4">
-        <v>5.095821896</v>
+        <v>5.077872844</v>
       </c>
       <c r="P4">
-        <v>18.067004904</v>
+        <v>18.003367356</v>
       </c>
       <c r="Q4">
-        <v>18.241004904</v>
+        <v>18.177367356</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08025758856455717</v>
+        <v>0.08053589475178462</v>
       </c>
       <c r="T4">
-        <v>0.5013998989090301</v>
+        <v>0.5054495930389652</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>142.9523965945388</v>
+        <v>95.30159772969255</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07929683790923107</v>
+        <v>0.07915655902519614</v>
       </c>
       <c r="C5">
-        <v>162.7045952484197</v>
+        <v>161.7414957938168</v>
       </c>
       <c r="D5">
-        <v>166.3705952484197</v>
+        <v>167.0294957938168</v>
       </c>
       <c r="E5">
-        <v>-22.234</v>
+        <v>-20.612</v>
       </c>
       <c r="F5">
-        <v>4.866</v>
+        <v>6.488</v>
       </c>
       <c r="G5">
         <v>1.2</v>
@@ -1685,28 +1685,28 @@
         <v>23.326</v>
       </c>
       <c r="M5">
-        <v>0.2447598</v>
+        <v>0.3263464</v>
       </c>
       <c r="N5">
-        <v>23.0812402</v>
+        <v>22.9996536</v>
       </c>
       <c r="O5">
-        <v>5.077872844</v>
+        <v>5.059923792</v>
       </c>
       <c r="P5">
-        <v>18.003367356</v>
+        <v>17.939729808</v>
       </c>
       <c r="Q5">
-        <v>18.177367356</v>
+        <v>18.113729808</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08053589475178462</v>
+        <v>0.08081999898457931</v>
       </c>
       <c r="T5">
-        <v>0.5054495930389652</v>
+        <v>0.5095836557966072</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>95.30159772969255</v>
+        <v>71.47619829726942</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07915655902519614</v>
+        <v>0.07901628014116119</v>
       </c>
       <c r="C6">
-        <v>161.7414957938168</v>
+        <v>160.7836361616598</v>
       </c>
       <c r="D6">
-        <v>167.0294957938168</v>
+        <v>167.6936361616598</v>
       </c>
       <c r="E6">
-        <v>-20.612</v>
+        <v>-18.99</v>
       </c>
       <c r="F6">
-        <v>6.488</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G6">
         <v>1.2</v>
@@ -1767,28 +1767,28 @@
         <v>23.326</v>
       </c>
       <c r="M6">
-        <v>0.3263464</v>
+        <v>0.4079329999999999</v>
       </c>
       <c r="N6">
-        <v>22.9996536</v>
+        <v>22.918067</v>
       </c>
       <c r="O6">
-        <v>5.059923792</v>
+        <v>5.041974740000001</v>
       </c>
       <c r="P6">
-        <v>17.939729808</v>
+        <v>17.87609226</v>
       </c>
       <c r="Q6">
-        <v>18.113729808</v>
+        <v>18.05009226</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08081999898457931</v>
+        <v>0.08111008435911705</v>
       </c>
       <c r="T6">
-        <v>0.5095836557966072</v>
+        <v>0.5138047514544102</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>71.47619829726942</v>
+        <v>57.18095863781554</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07901628014116119</v>
+        <v>0.07887600125712625</v>
       </c>
       <c r="C7">
-        <v>160.7836361616598</v>
+        <v>159.8310791049948</v>
       </c>
       <c r="D7">
-        <v>167.6936361616598</v>
+        <v>168.3630791049948</v>
       </c>
       <c r="E7">
-        <v>-18.99</v>
+        <v>-17.368</v>
       </c>
       <c r="F7">
-        <v>8.109999999999999</v>
+        <v>9.731999999999999</v>
       </c>
       <c r="G7">
         <v>1.2</v>
@@ -1849,28 +1849,28 @@
         <v>23.326</v>
       </c>
       <c r="M7">
-        <v>0.4079329999999999</v>
+        <v>0.4895195999999999</v>
       </c>
       <c r="N7">
-        <v>22.918067</v>
+        <v>22.8364804</v>
       </c>
       <c r="O7">
-        <v>5.041974740000001</v>
+        <v>5.024025688</v>
       </c>
       <c r="P7">
-        <v>17.87609226</v>
+        <v>17.812454712</v>
       </c>
       <c r="Q7">
-        <v>18.05009226</v>
+        <v>17.986454712</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08111008435911705</v>
+        <v>0.08140634176290028</v>
       </c>
       <c r="T7">
-        <v>0.5138047514544102</v>
+        <v>0.5181156576581237</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>57.18095863781554</v>
+        <v>47.65079886484627</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07887600125712625</v>
+        <v>0.07873572237309132</v>
       </c>
       <c r="C8">
-        <v>159.8310791049948</v>
+        <v>158.8838883829396</v>
       </c>
       <c r="D8">
-        <v>168.3630791049948</v>
+        <v>169.0378883829396</v>
       </c>
       <c r="E8">
-        <v>-17.368</v>
+        <v>-15.746</v>
       </c>
       <c r="F8">
-        <v>9.731999999999999</v>
+        <v>11.354</v>
       </c>
       <c r="G8">
         <v>1.2</v>
@@ -1931,28 +1931,28 @@
         <v>23.326</v>
       </c>
       <c r="M8">
-        <v>0.4895195999999999</v>
+        <v>0.5711061999999999</v>
       </c>
       <c r="N8">
-        <v>22.8364804</v>
+        <v>22.7548938</v>
       </c>
       <c r="O8">
-        <v>5.024025688</v>
+        <v>5.006076636</v>
       </c>
       <c r="P8">
-        <v>17.812454712</v>
+        <v>17.748817164</v>
       </c>
       <c r="Q8">
-        <v>17.986454712</v>
+        <v>17.922817164</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08140634176290028</v>
+        <v>0.08170897029364659</v>
       </c>
       <c r="T8">
-        <v>0.5181156576581237</v>
+        <v>0.5225192715221323</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>47.65079886484627</v>
+        <v>40.84354188415396</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07873572237309134</v>
+        <v>0.07859544348905639</v>
       </c>
       <c r="C9">
-        <v>158.8838883829395</v>
+        <v>157.9421287809272</v>
       </c>
       <c r="D9">
-        <v>169.0378883829395</v>
+        <v>169.7181287809272</v>
       </c>
       <c r="E9">
-        <v>-15.746</v>
+        <v>-14.124</v>
       </c>
       <c r="F9">
-        <v>11.354</v>
+        <v>12.976</v>
       </c>
       <c r="G9">
         <v>1.2</v>
@@ -2013,28 +2013,28 @@
         <v>23.326</v>
       </c>
       <c r="M9">
-        <v>0.5711062</v>
+        <v>0.6526928</v>
       </c>
       <c r="N9">
-        <v>22.7548938</v>
+        <v>22.6733072</v>
       </c>
       <c r="O9">
-        <v>5.006076636</v>
+        <v>4.988127584</v>
       </c>
       <c r="P9">
-        <v>17.748817164</v>
+        <v>17.685179616</v>
       </c>
       <c r="Q9">
-        <v>17.922817164</v>
+        <v>17.859179616</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0817089702936466</v>
+        <v>0.08201817770549608</v>
       </c>
       <c r="T9">
-        <v>0.5225192715221324</v>
+        <v>0.5270186161223149</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>40.84354188415395</v>
+        <v>35.7380991486347</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07859544348905639</v>
+        <v>0.07845516460502146</v>
       </c>
       <c r="C10">
-        <v>157.9421287809272</v>
+        <v>157.0058661314393</v>
       </c>
       <c r="D10">
-        <v>169.7181287809272</v>
+        <v>170.4038661314394</v>
       </c>
       <c r="E10">
-        <v>-14.124</v>
+        <v>-12.502</v>
       </c>
       <c r="F10">
-        <v>12.976</v>
+        <v>14.598</v>
       </c>
       <c r="G10">
         <v>1.2</v>
@@ -2095,28 +2095,28 @@
         <v>23.326</v>
       </c>
       <c r="M10">
-        <v>0.6526928</v>
+        <v>0.7342793999999999</v>
       </c>
       <c r="N10">
-        <v>22.6733072</v>
+        <v>22.5917206</v>
       </c>
       <c r="O10">
-        <v>4.988127584</v>
+        <v>4.970178532</v>
       </c>
       <c r="P10">
-        <v>17.685179616</v>
+        <v>17.621542068</v>
       </c>
       <c r="Q10">
-        <v>17.859179616</v>
+        <v>17.795542068</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08201817770549608</v>
+        <v>0.08233418088463895</v>
       </c>
       <c r="T10">
-        <v>0.5270186161223149</v>
+        <v>0.5316168474170071</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>35.7380991486347</v>
+        <v>31.76719924323085</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07845516460502146</v>
+        <v>0.07831488572098649</v>
       </c>
       <c r="C11">
-        <v>157.0058661314393</v>
+        <v>156.0751673352452</v>
       </c>
       <c r="D11">
-        <v>170.4038661314394</v>
+        <v>171.0951673352452</v>
       </c>
       <c r="E11">
-        <v>-12.502</v>
+        <v>-10.88</v>
       </c>
       <c r="F11">
-        <v>14.598</v>
+        <v>16.22</v>
       </c>
       <c r="G11">
         <v>1.2</v>
@@ -2177,28 +2177,28 @@
         <v>23.326</v>
       </c>
       <c r="M11">
-        <v>0.7342793999999999</v>
+        <v>0.8158659999999999</v>
       </c>
       <c r="N11">
-        <v>22.5917206</v>
+        <v>22.510134</v>
       </c>
       <c r="O11">
-        <v>4.970178532</v>
+        <v>4.952229480000001</v>
       </c>
       <c r="P11">
-        <v>17.621542068</v>
+        <v>17.55790452</v>
       </c>
       <c r="Q11">
-        <v>17.795542068</v>
+        <v>17.73190452</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08233418088463895</v>
+        <v>0.08265720635665166</v>
       </c>
       <c r="T11">
-        <v>0.5316168474170071</v>
+        <v>0.536317261629359</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>31.76719924323085</v>
+        <v>28.59047931890777</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07831488572098649</v>
+        <v>0.07817460683695157</v>
       </c>
       <c r="C12">
-        <v>156.0751673352452</v>
+        <v>155.1501003831584</v>
       </c>
       <c r="D12">
-        <v>171.0951673352452</v>
+        <v>171.7921003831584</v>
       </c>
       <c r="E12">
-        <v>-10.88</v>
+        <v>-9.258000000000003</v>
       </c>
       <c r="F12">
-        <v>16.22</v>
+        <v>17.842</v>
       </c>
       <c r="G12">
         <v>1.2</v>
@@ -2259,28 +2259,28 @@
         <v>23.326</v>
       </c>
       <c r="M12">
-        <v>0.8158659999999999</v>
+        <v>0.8974525999999999</v>
       </c>
       <c r="N12">
-        <v>22.510134</v>
+        <v>22.4285474</v>
       </c>
       <c r="O12">
-        <v>4.952229480000001</v>
+        <v>4.934280428</v>
       </c>
       <c r="P12">
-        <v>17.55790452</v>
+        <v>17.494266972</v>
       </c>
       <c r="Q12">
-        <v>17.73190452</v>
+        <v>17.668266972</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08265720635665166</v>
+        <v>0.08298749082803547</v>
       </c>
       <c r="T12">
-        <v>0.536317261629359</v>
+        <v>0.5411233031273819</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>28.59047931890777</v>
+        <v>25.99134483537069</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07817460683695157</v>
+        <v>0.07803432795291664</v>
       </c>
       <c r="C13">
-        <v>155.1501003831584</v>
+        <v>154.2307343783298</v>
       </c>
       <c r="D13">
-        <v>171.7921003831584</v>
+        <v>172.4947343783298</v>
       </c>
       <c r="E13">
-        <v>-9.258000000000003</v>
+        <v>-7.636000000000003</v>
       </c>
       <c r="F13">
-        <v>17.842</v>
+        <v>19.464</v>
       </c>
       <c r="G13">
         <v>1.2</v>
@@ -2341,28 +2341,28 @@
         <v>23.326</v>
       </c>
       <c r="M13">
-        <v>0.8974525999999999</v>
+        <v>0.9790391999999999</v>
       </c>
       <c r="N13">
-        <v>22.4285474</v>
+        <v>22.3469608</v>
       </c>
       <c r="O13">
-        <v>4.934280428</v>
+        <v>4.916331376</v>
       </c>
       <c r="P13">
-        <v>17.494266972</v>
+        <v>17.430629424</v>
       </c>
       <c r="Q13">
-        <v>17.668266972</v>
+        <v>17.604629424</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08298749082803547</v>
+        <v>0.08332528176467799</v>
       </c>
       <c r="T13">
-        <v>0.5411233031273819</v>
+        <v>0.5460385728412688</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>25.99134483537069</v>
+        <v>23.82539943242314</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07803432795291664</v>
+        <v>0.07789404906888167</v>
       </c>
       <c r="C14">
-        <v>154.2307343783298</v>
+        <v>153.3171395590874</v>
       </c>
       <c r="D14">
-        <v>172.4947343783298</v>
+        <v>173.2031395590874</v>
       </c>
       <c r="E14">
-        <v>-7.636000000000003</v>
+        <v>-6.014000000000003</v>
       </c>
       <c r="F14">
-        <v>19.464</v>
+        <v>21.086</v>
       </c>
       <c r="G14">
         <v>1.2</v>
@@ -2423,28 +2423,28 @@
         <v>23.326</v>
       </c>
       <c r="M14">
-        <v>0.9790391999999999</v>
+        <v>1.0606258</v>
       </c>
       <c r="N14">
-        <v>22.3469608</v>
+        <v>22.2653742</v>
       </c>
       <c r="O14">
-        <v>4.916331376</v>
+        <v>4.898382324</v>
       </c>
       <c r="P14">
-        <v>17.430629424</v>
+        <v>17.366991876</v>
       </c>
       <c r="Q14">
-        <v>17.604629424</v>
+        <v>17.540991876</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08332528176467799</v>
+        <v>0.08367083801020883</v>
       </c>
       <c r="T14">
-        <v>0.5460385728412688</v>
+        <v>0.5510668372612221</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.82539943242314</v>
+        <v>21.99267639915982</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07789404906888167</v>
+        <v>0.07775377018484675</v>
       </c>
       <c r="C15">
-        <v>153.3171395590874</v>
+        <v>152.409387322342</v>
       </c>
       <c r="D15">
-        <v>173.2031395590874</v>
+        <v>173.917387322342</v>
       </c>
       <c r="E15">
-        <v>-6.014000000000003</v>
+        <v>-4.391999999999999</v>
       </c>
       <c r="F15">
-        <v>21.086</v>
+        <v>22.708</v>
       </c>
       <c r="G15">
         <v>1.2</v>
@@ -2505,28 +2505,28 @@
         <v>23.326</v>
       </c>
       <c r="M15">
-        <v>1.0606258</v>
+        <v>1.1422124</v>
       </c>
       <c r="N15">
-        <v>22.2653742</v>
+        <v>22.1837876</v>
       </c>
       <c r="O15">
-        <v>4.898382324</v>
+        <v>4.880433272</v>
       </c>
       <c r="P15">
-        <v>17.366991876</v>
+        <v>17.303354328</v>
       </c>
       <c r="Q15">
-        <v>17.540991876</v>
+        <v>17.477354328</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08367083801020883</v>
+        <v>0.08402443044749622</v>
       </c>
       <c r="T15">
-        <v>0.5510668372612221</v>
+        <v>0.5562120380630348</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.99267639915982</v>
+        <v>20.42177094207698</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07775377018484675</v>
+        <v>0.07761349130081181</v>
       </c>
       <c r="C16">
-        <v>152.409387322342</v>
+        <v>151.5075502475762</v>
       </c>
       <c r="D16">
-        <v>173.917387322342</v>
+        <v>174.6375502475762</v>
       </c>
       <c r="E16">
-        <v>-4.391999999999999</v>
+        <v>-2.77</v>
       </c>
       <c r="F16">
-        <v>22.708</v>
+        <v>24.33</v>
       </c>
       <c r="G16">
         <v>1.2</v>
@@ -2587,28 +2587,28 @@
         <v>23.326</v>
       </c>
       <c r="M16">
-        <v>1.1422124</v>
+        <v>1.223799</v>
       </c>
       <c r="N16">
-        <v>22.1837876</v>
+        <v>22.102201</v>
       </c>
       <c r="O16">
-        <v>4.880433272</v>
+        <v>4.86248422</v>
       </c>
       <c r="P16">
-        <v>17.303354328</v>
+        <v>17.23971678</v>
       </c>
       <c r="Q16">
-        <v>17.477354328</v>
+        <v>17.41371678</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08402443044749622</v>
+        <v>0.08438634270683742</v>
       </c>
       <c r="T16">
-        <v>0.5562120380630348</v>
+        <v>0.5614783024131255</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.42177094207698</v>
+        <v>19.06031954593851</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07761349130081181</v>
+        <v>0.07747321241677688</v>
       </c>
       <c r="C17">
-        <v>151.5075502475762</v>
+        <v>150.6117021214288</v>
       </c>
       <c r="D17">
-        <v>174.6375502475762</v>
+        <v>175.3637021214288</v>
       </c>
       <c r="E17">
-        <v>-2.770000000000003</v>
+        <v>-1.148000000000003</v>
       </c>
       <c r="F17">
-        <v>24.33</v>
+        <v>25.952</v>
       </c>
       <c r="G17">
         <v>1.2</v>
@@ -2669,28 +2669,28 @@
         <v>23.326</v>
       </c>
       <c r="M17">
-        <v>1.223799</v>
+        <v>1.3053856</v>
       </c>
       <c r="N17">
-        <v>22.102201</v>
+        <v>22.0206144</v>
       </c>
       <c r="O17">
-        <v>4.86248422</v>
+        <v>4.844535168</v>
       </c>
       <c r="P17">
-        <v>17.23971678</v>
+        <v>17.176079232</v>
       </c>
       <c r="Q17">
-        <v>17.41371678</v>
+        <v>17.350079232</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08438634270683742</v>
+        <v>0.08475687192473438</v>
       </c>
       <c r="T17">
-        <v>0.5614783024131255</v>
+        <v>0.5668699540096468</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.06031954593851</v>
+        <v>17.86904957431735</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07747321241677688</v>
+        <v>0.07733293353274193</v>
       </c>
       <c r="C18">
-        <v>150.6117021214288</v>
+        <v>149.7219179628974</v>
       </c>
       <c r="D18">
-        <v>175.3637021214288</v>
+        <v>176.0959179628975</v>
       </c>
       <c r="E18">
-        <v>-1.148000000000003</v>
+        <v>0.4740000000000002</v>
       </c>
       <c r="F18">
-        <v>25.952</v>
+        <v>27.574</v>
       </c>
       <c r="G18">
         <v>1.2</v>
@@ -2751,28 +2751,28 @@
         <v>23.326</v>
       </c>
       <c r="M18">
-        <v>1.3053856</v>
+        <v>1.3869722</v>
       </c>
       <c r="N18">
-        <v>22.0206144</v>
+        <v>21.9390278</v>
       </c>
       <c r="O18">
-        <v>4.844535168</v>
+        <v>4.826586116000001</v>
       </c>
       <c r="P18">
-        <v>17.176079232</v>
+        <v>17.112441684</v>
       </c>
       <c r="Q18">
-        <v>17.350079232</v>
+        <v>17.286441684</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08475687192473438</v>
+        <v>0.0851363295575204</v>
       </c>
       <c r="T18">
-        <v>0.5668699540096468</v>
+        <v>0.5723915249217471</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.86904957431735</v>
+        <v>16.81792901112221</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07733293353274193</v>
+        <v>0.077192654648707</v>
       </c>
       <c r="C19">
-        <v>149.7219179628974</v>
+        <v>148.8382740491743</v>
       </c>
       <c r="D19">
-        <v>176.0959179628975</v>
+        <v>176.8342740491743</v>
       </c>
       <c r="E19">
-        <v>0.4740000000000002</v>
+        <v>2.096</v>
       </c>
       <c r="F19">
-        <v>27.574</v>
+        <v>29.196</v>
       </c>
       <c r="G19">
         <v>1.2</v>
@@ -2833,28 +2833,28 @@
         <v>23.326</v>
       </c>
       <c r="M19">
-        <v>1.3869722</v>
+        <v>1.4685588</v>
       </c>
       <c r="N19">
-        <v>21.9390278</v>
+        <v>21.8574412</v>
       </c>
       <c r="O19">
-        <v>4.826586116000001</v>
+        <v>4.808637064</v>
       </c>
       <c r="P19">
-        <v>17.112441684</v>
+        <v>17.048804136</v>
       </c>
       <c r="Q19">
-        <v>17.286441684</v>
+        <v>17.222804136</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0851363295575204</v>
+        <v>0.08552504225452073</v>
       </c>
       <c r="T19">
-        <v>0.5723915249217471</v>
+        <v>0.5780477682951179</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.81792901112221</v>
+        <v>15.88359962161542</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.077192654648707</v>
+        <v>0.07705237576467205</v>
       </c>
       <c r="C20">
-        <v>148.8382740491743</v>
+        <v>147.960847942135</v>
       </c>
       <c r="D20">
-        <v>176.8342740491743</v>
+        <v>177.5788479421351</v>
       </c>
       <c r="E20">
-        <v>2.095999999999997</v>
+        <v>3.717999999999996</v>
       </c>
       <c r="F20">
-        <v>29.196</v>
+        <v>30.818</v>
       </c>
       <c r="G20">
         <v>1.2</v>
@@ -2915,28 +2915,28 @@
         <v>23.326</v>
       </c>
       <c r="M20">
-        <v>1.4685588</v>
+        <v>1.5501454</v>
       </c>
       <c r="N20">
-        <v>21.8574412</v>
+        <v>21.7758546</v>
       </c>
       <c r="O20">
-        <v>4.808637064</v>
+        <v>4.790688012</v>
       </c>
       <c r="P20">
-        <v>17.048804136</v>
+        <v>16.985166588</v>
       </c>
       <c r="Q20">
-        <v>17.222804136</v>
+        <v>17.159166588</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08552504225452072</v>
+        <v>0.08592335279589143</v>
       </c>
       <c r="T20">
-        <v>0.5780477682951178</v>
+        <v>0.5838436719986956</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.88359962161542</v>
+        <v>15.04762069416198</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07705237576467205</v>
+        <v>0.07691209688063712</v>
       </c>
       <c r="C21">
-        <v>147.960847942135</v>
+        <v>147.0897185154988</v>
       </c>
       <c r="D21">
-        <v>177.5788479421351</v>
+        <v>178.3297185154988</v>
       </c>
       <c r="E21">
-        <v>3.717999999999996</v>
+        <v>5.339999999999996</v>
       </c>
       <c r="F21">
-        <v>30.818</v>
+        <v>32.44</v>
       </c>
       <c r="G21">
         <v>1.2</v>
@@ -2997,28 +2997,28 @@
         <v>23.326</v>
       </c>
       <c r="M21">
-        <v>1.5501454</v>
+        <v>1.631732</v>
       </c>
       <c r="N21">
-        <v>21.7758546</v>
+        <v>21.694268</v>
       </c>
       <c r="O21">
-        <v>4.790688012</v>
+        <v>4.77273896</v>
       </c>
       <c r="P21">
-        <v>16.985166588</v>
+        <v>16.92152904</v>
       </c>
       <c r="Q21">
-        <v>17.159166588</v>
+        <v>17.09552904</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08592335279589143</v>
+        <v>0.0863316211007964</v>
       </c>
       <c r="T21">
-        <v>0.5838436719986956</v>
+        <v>0.5897844732948626</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.04762069416198</v>
+        <v>14.29523965945388</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07691209688063712</v>
+        <v>0.07677181799660218</v>
       </c>
       <c r="C22">
-        <v>147.0897185154988</v>
+        <v>146.2249659826815</v>
       </c>
       <c r="D22">
-        <v>178.3297185154988</v>
+        <v>179.0869659826814</v>
       </c>
       <c r="E22">
-        <v>5.339999999999996</v>
+        <v>6.961999999999996</v>
       </c>
       <c r="F22">
-        <v>32.44</v>
+        <v>34.062</v>
       </c>
       <c r="G22">
         <v>1.2</v>
@@ -3079,28 +3079,28 @@
         <v>23.326</v>
       </c>
       <c r="M22">
-        <v>1.631732</v>
+        <v>1.7133186</v>
       </c>
       <c r="N22">
-        <v>21.694268</v>
+        <v>21.6126814</v>
       </c>
       <c r="O22">
-        <v>4.77273896</v>
+        <v>4.754789908</v>
       </c>
       <c r="P22">
-        <v>16.92152904</v>
+        <v>16.857891492</v>
       </c>
       <c r="Q22">
-        <v>17.09552904</v>
+        <v>17.031891492</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0863316211007964</v>
+        <v>0.08675022531215465</v>
       </c>
       <c r="T22">
-        <v>0.5897844732948626</v>
+        <v>0.5958756746238441</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.29523965945388</v>
+        <v>13.61451396138465</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07677181799660218</v>
+        <v>0.07663153911256723</v>
       </c>
       <c r="C23">
-        <v>146.2249659826815</v>
+        <v>145.3666719253606</v>
       </c>
       <c r="D23">
-        <v>179.0869659826814</v>
+        <v>179.8506719253606</v>
       </c>
       <c r="E23">
-        <v>6.961999999999996</v>
+        <v>8.583999999999996</v>
       </c>
       <c r="F23">
-        <v>34.062</v>
+        <v>35.684</v>
       </c>
       <c r="G23">
         <v>1.2</v>
@@ -3161,28 +3161,28 @@
         <v>23.326</v>
       </c>
       <c r="M23">
-        <v>1.7133186</v>
+        <v>1.7949052</v>
       </c>
       <c r="N23">
-        <v>21.6126814</v>
+        <v>21.5310948</v>
       </c>
       <c r="O23">
-        <v>4.754789908</v>
+        <v>4.736840856000001</v>
       </c>
       <c r="P23">
-        <v>16.857891492</v>
+        <v>16.794253944</v>
       </c>
       <c r="Q23">
-        <v>17.031891492</v>
+        <v>16.968253944</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08675022531215465</v>
+        <v>0.08717956296482979</v>
       </c>
       <c r="T23">
-        <v>0.5958756746238439</v>
+        <v>0.6021230606022865</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.61451396138465</v>
+        <v>12.99567241768535</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07663153911256723</v>
+        <v>0.0767603602285323</v>
       </c>
       <c r="C24">
-        <v>145.3666719253606</v>
+        <v>143.0431010056432</v>
       </c>
       <c r="D24">
-        <v>179.8506719253606</v>
+        <v>179.1491010056432</v>
       </c>
       <c r="E24">
-        <v>8.583999999999996</v>
+        <v>10.206</v>
       </c>
       <c r="F24">
-        <v>35.684</v>
+        <v>37.306</v>
       </c>
       <c r="G24">
         <v>1.2</v>
@@ -3243,45 +3243,45 @@
         <v>23.326</v>
       </c>
       <c r="M24">
-        <v>1.7949052</v>
+        <v>1.9324508</v>
       </c>
       <c r="N24">
-        <v>21.5310948</v>
+        <v>21.3935492</v>
       </c>
       <c r="O24">
-        <v>4.736840856000001</v>
+        <v>4.706580824</v>
       </c>
       <c r="P24">
-        <v>16.794253944</v>
+        <v>16.686968376</v>
       </c>
       <c r="Q24">
-        <v>16.968253944</v>
+        <v>16.860968376</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08717956296482979</v>
+        <v>0.08762005224484715</v>
       </c>
       <c r="T24">
-        <v>0.6021230606022865</v>
+        <v>0.6085327163464028</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>12.99567241768535</v>
+        <v>12.07068247222646</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0767603602285323</v>
+        <v>0.07663178134449737</v>
       </c>
       <c r="C25">
-        <v>143.0431010056432</v>
+        <v>142.1213475528881</v>
       </c>
       <c r="D25">
-        <v>179.1491010056432</v>
+        <v>179.8493475528881</v>
       </c>
       <c r="E25">
-        <v>10.206</v>
+        <v>11.828</v>
       </c>
       <c r="F25">
-        <v>37.306</v>
+        <v>38.928</v>
       </c>
       <c r="G25">
         <v>1.2</v>
@@ -3325,28 +3325,28 @@
         <v>23.326</v>
       </c>
       <c r="M25">
-        <v>1.9324508</v>
+        <v>2.0164704</v>
       </c>
       <c r="N25">
-        <v>21.3935492</v>
+        <v>21.3095296</v>
       </c>
       <c r="O25">
-        <v>4.706580824</v>
+        <v>4.688096512</v>
       </c>
       <c r="P25">
-        <v>16.686968376</v>
+        <v>16.621433088</v>
       </c>
       <c r="Q25">
-        <v>16.860968376</v>
+        <v>16.795433088</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08762005224484715</v>
+        <v>0.08807213334802284</v>
       </c>
       <c r="T25">
-        <v>0.6085327163464028</v>
+        <v>0.6151110472416801</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.07068247222646</v>
+        <v>11.56773736921703</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07663178134449737</v>
+        <v>0.07650320246046241</v>
       </c>
       <c r="C26">
-        <v>142.1213475528881</v>
+        <v>141.2050897389638</v>
       </c>
       <c r="D26">
-        <v>179.8493475528881</v>
+        <v>180.5550897389638</v>
       </c>
       <c r="E26">
-        <v>11.828</v>
+        <v>13.45</v>
       </c>
       <c r="F26">
-        <v>38.928</v>
+        <v>40.55</v>
       </c>
       <c r="G26">
         <v>1.2</v>
@@ -3407,28 +3407,28 @@
         <v>23.326</v>
       </c>
       <c r="M26">
-        <v>2.0164704</v>
+        <v>2.10049</v>
       </c>
       <c r="N26">
-        <v>21.3095296</v>
+        <v>21.22551</v>
       </c>
       <c r="O26">
-        <v>4.688096512</v>
+        <v>4.6696122</v>
       </c>
       <c r="P26">
-        <v>16.621433088</v>
+        <v>16.5558978</v>
       </c>
       <c r="Q26">
-        <v>16.795433088</v>
+        <v>16.7298978</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08807213334802284</v>
+        <v>0.08853626994728322</v>
       </c>
       <c r="T26">
-        <v>0.6151110472416801</v>
+        <v>0.6218648002941648</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.56773736921703</v>
+        <v>11.10502787444834</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07650320246046241</v>
+        <v>0.07637462357642749</v>
       </c>
       <c r="C27">
-        <v>141.2050897389638</v>
+        <v>140.2943925146254</v>
       </c>
       <c r="D27">
-        <v>180.5550897389638</v>
+        <v>181.2663925146254</v>
       </c>
       <c r="E27">
-        <v>13.45</v>
+        <v>15.072</v>
       </c>
       <c r="F27">
-        <v>40.55</v>
+        <v>42.172</v>
       </c>
       <c r="G27">
         <v>1.2</v>
@@ -3489,28 +3489,28 @@
         <v>23.326</v>
       </c>
       <c r="M27">
-        <v>2.10049</v>
+        <v>2.1845096</v>
       </c>
       <c r="N27">
-        <v>21.22551</v>
+        <v>21.1414904</v>
       </c>
       <c r="O27">
-        <v>4.6696122</v>
+        <v>4.651127888</v>
       </c>
       <c r="P27">
-        <v>16.5558978</v>
+        <v>16.490362512</v>
       </c>
       <c r="Q27">
-        <v>16.7298978</v>
+        <v>16.664362512</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08853626994728322</v>
+        <v>0.08901295077895606</v>
       </c>
       <c r="T27">
-        <v>0.6218648002941648</v>
+        <v>0.6288010872129328</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.10502787444834</v>
+        <v>10.67791141773879</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07637462357642749</v>
+        <v>0.07624604469239253</v>
       </c>
       <c r="C28">
-        <v>140.2943925146254</v>
+        <v>139.3893218581794</v>
       </c>
       <c r="D28">
-        <v>181.2663925146254</v>
+        <v>181.9833218581794</v>
       </c>
       <c r="E28">
-        <v>15.072</v>
+        <v>16.694</v>
       </c>
       <c r="F28">
-        <v>42.172</v>
+        <v>43.794</v>
       </c>
       <c r="G28">
         <v>1.2</v>
@@ -3571,28 +3571,28 @@
         <v>23.326</v>
       </c>
       <c r="M28">
-        <v>2.1845096</v>
+        <v>2.2685292</v>
       </c>
       <c r="N28">
-        <v>21.1414904</v>
+        <v>21.0574708</v>
       </c>
       <c r="O28">
-        <v>4.651127888</v>
+        <v>4.632643576</v>
       </c>
       <c r="P28">
-        <v>16.490362512</v>
+        <v>16.424827224</v>
       </c>
       <c r="Q28">
-        <v>16.664362512</v>
+        <v>16.598827224</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08901295077895606</v>
+        <v>0.08950269135944183</v>
       </c>
       <c r="T28">
-        <v>0.6288010872129328</v>
+        <v>0.6359274093897492</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.67791141773879</v>
+        <v>10.2824332170818</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07624604469239253</v>
+        <v>0.07611746580835761</v>
       </c>
       <c r="C29">
-        <v>139.3893218581794</v>
+        <v>138.4899447958831</v>
       </c>
       <c r="D29">
-        <v>181.9833218581794</v>
+        <v>182.7059447958831</v>
       </c>
       <c r="E29">
-        <v>16.694</v>
+        <v>18.316</v>
       </c>
       <c r="F29">
-        <v>43.794</v>
+        <v>45.416</v>
       </c>
       <c r="G29">
         <v>1.2</v>
@@ -3653,28 +3653,28 @@
         <v>23.326</v>
       </c>
       <c r="M29">
-        <v>2.2685292</v>
+        <v>2.3525488</v>
       </c>
       <c r="N29">
-        <v>21.0574708</v>
+        <v>20.9734512</v>
       </c>
       <c r="O29">
-        <v>4.632643576</v>
+        <v>4.614159264</v>
       </c>
       <c r="P29">
-        <v>16.424827224</v>
+        <v>16.359291936</v>
       </c>
       <c r="Q29">
-        <v>16.598827224</v>
+        <v>16.533291936</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08950269135944183</v>
+        <v>0.09000603584494113</v>
       </c>
       <c r="T29">
-        <v>0.6359274093897492</v>
+        <v>0.6432516849603662</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.2824332170818</v>
+        <v>9.915203459328877</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07611746580835761</v>
+        <v>0.07637342692432267</v>
       </c>
       <c r="C30">
-        <v>138.4899447958831</v>
+        <v>135.4350387579939</v>
       </c>
       <c r="D30">
-        <v>182.7059447958831</v>
+        <v>181.273038757994</v>
       </c>
       <c r="E30">
-        <v>18.316</v>
+        <v>19.938</v>
       </c>
       <c r="F30">
-        <v>45.416</v>
+        <v>47.038</v>
       </c>
       <c r="G30">
         <v>1.2</v>
@@ -3735,45 +3735,45 @@
         <v>23.326</v>
       </c>
       <c r="M30">
-        <v>2.3525488</v>
+        <v>2.516533</v>
       </c>
       <c r="N30">
-        <v>20.9734512</v>
+        <v>20.809467</v>
       </c>
       <c r="O30">
-        <v>4.614159264</v>
+        <v>4.57808274</v>
       </c>
       <c r="P30">
-        <v>16.359291936</v>
+        <v>16.23138426</v>
       </c>
       <c r="Q30">
-        <v>16.533291936</v>
+        <v>16.40538426</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09000603584494113</v>
+        <v>0.09052355904834178</v>
       </c>
       <c r="T30">
-        <v>0.6432516849603662</v>
+        <v>0.6507822781526906</v>
       </c>
       <c r="U30">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V30">
         <v>0.22</v>
       </c>
       <c r="W30">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>9.915203459328877</v>
+        <v>9.269101577448021</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07637342692432267</v>
+        <v>0.07625810804028772</v>
       </c>
       <c r="C31">
-        <v>135.4350387579939</v>
+        <v>134.4558181347055</v>
       </c>
       <c r="D31">
-        <v>181.273038757994</v>
+        <v>181.9158181347055</v>
       </c>
       <c r="E31">
-        <v>19.938</v>
+        <v>21.56</v>
       </c>
       <c r="F31">
-        <v>47.038</v>
+        <v>48.66</v>
       </c>
       <c r="G31">
         <v>1.2</v>
@@ -3817,28 +3817,28 @@
         <v>23.326</v>
       </c>
       <c r="M31">
-        <v>2.516533</v>
+        <v>2.60331</v>
       </c>
       <c r="N31">
-        <v>20.809467</v>
+        <v>20.72269</v>
       </c>
       <c r="O31">
-        <v>4.57808274</v>
+        <v>4.5589918</v>
       </c>
       <c r="P31">
-        <v>16.23138426</v>
+        <v>16.1636982</v>
       </c>
       <c r="Q31">
-        <v>16.40538426</v>
+        <v>16.3376982</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09052355904834178</v>
+        <v>0.09105586862898246</v>
       </c>
       <c r="T31">
-        <v>0.6507822781526906</v>
+        <v>0.6585280311505101</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.269101577448021</v>
+        <v>8.960131524866421</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07625810804028772</v>
+        <v>0.07614278915625279</v>
       </c>
       <c r="C32">
-        <v>134.4558181347055</v>
+        <v>133.4811722192045</v>
       </c>
       <c r="D32">
-        <v>181.9158181347055</v>
+        <v>182.5631722192045</v>
       </c>
       <c r="E32">
-        <v>21.56</v>
+        <v>23.182</v>
       </c>
       <c r="F32">
-        <v>48.66</v>
+        <v>50.282</v>
       </c>
       <c r="G32">
         <v>1.2</v>
@@ -3899,28 +3899,28 @@
         <v>23.326</v>
       </c>
       <c r="M32">
-        <v>2.60331</v>
+        <v>2.690087</v>
       </c>
       <c r="N32">
-        <v>20.72269</v>
+        <v>20.635913</v>
       </c>
       <c r="O32">
-        <v>4.5589918</v>
+        <v>4.53990086</v>
       </c>
       <c r="P32">
-        <v>16.1636982</v>
+        <v>16.09601214</v>
       </c>
       <c r="Q32">
-        <v>16.3376982</v>
+        <v>16.27001214</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09105586862898246</v>
+        <v>0.09160360747283014</v>
       </c>
       <c r="T32">
-        <v>0.6585280311505101</v>
+        <v>0.6664982987279765</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.960131524866421</v>
+        <v>8.671095024064279</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07614278915625279</v>
+        <v>0.07602747027221786</v>
       </c>
       <c r="C33">
-        <v>133.4811722192045</v>
+        <v>132.5111500236971</v>
       </c>
       <c r="D33">
-        <v>182.5631722192045</v>
+        <v>183.2151500236971</v>
       </c>
       <c r="E33">
-        <v>23.182</v>
+        <v>24.80399999999999</v>
       </c>
       <c r="F33">
-        <v>50.282</v>
+        <v>51.904</v>
       </c>
       <c r="G33">
         <v>1.2</v>
@@ -3981,28 +3981,28 @@
         <v>23.326</v>
       </c>
       <c r="M33">
-        <v>2.690087</v>
+        <v>2.776864</v>
       </c>
       <c r="N33">
-        <v>20.635913</v>
+        <v>20.549136</v>
       </c>
       <c r="O33">
-        <v>4.53990086</v>
+        <v>4.52080992</v>
       </c>
       <c r="P33">
-        <v>16.09601214</v>
+        <v>16.02832608</v>
       </c>
       <c r="Q33">
-        <v>16.27001214</v>
+        <v>16.20232608</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09160360747283014</v>
+        <v>0.09216745628267331</v>
       </c>
       <c r="T33">
-        <v>0.6664982987279765</v>
+        <v>0.6747029859400743</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.671095024064279</v>
+        <v>8.400123304562269</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07602747027221786</v>
+        <v>0.0759121513881829</v>
       </c>
       <c r="C34">
-        <v>132.5111500236971</v>
+        <v>131.5458012630372</v>
       </c>
       <c r="D34">
-        <v>183.2151500236971</v>
+        <v>183.8718012630372</v>
       </c>
       <c r="E34">
-        <v>24.80399999999999</v>
+        <v>26.42599999999999</v>
       </c>
       <c r="F34">
-        <v>51.904</v>
+        <v>53.526</v>
       </c>
       <c r="G34">
         <v>1.2</v>
@@ -4063,28 +4063,28 @@
         <v>23.326</v>
       </c>
       <c r="M34">
-        <v>2.776864</v>
+        <v>2.863641</v>
       </c>
       <c r="N34">
-        <v>20.549136</v>
+        <v>20.462359</v>
       </c>
       <c r="O34">
-        <v>4.52080992</v>
+        <v>4.50171898</v>
       </c>
       <c r="P34">
-        <v>16.02832608</v>
+        <v>15.96064002</v>
       </c>
       <c r="Q34">
-        <v>16.20232608</v>
+        <v>16.13464002</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09216745628267331</v>
+        <v>0.092748136400273</v>
       </c>
       <c r="T34">
-        <v>0.6747029859400743</v>
+        <v>0.683152589188354</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.400123304562269</v>
+        <v>8.145574113514927</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0759121513881829</v>
+        <v>0.07579683250414797</v>
       </c>
       <c r="C35">
-        <v>131.5458012630372</v>
+        <v>130.5851763673628</v>
       </c>
       <c r="D35">
-        <v>183.8718012630372</v>
+        <v>184.5331763673628</v>
       </c>
       <c r="E35">
-        <v>26.42599999999999</v>
+        <v>28.048</v>
       </c>
       <c r="F35">
-        <v>53.526</v>
+        <v>55.148</v>
       </c>
       <c r="G35">
         <v>1.2</v>
@@ -4145,28 +4145,28 @@
         <v>23.326</v>
       </c>
       <c r="M35">
-        <v>2.863641</v>
+        <v>2.950418</v>
       </c>
       <c r="N35">
-        <v>20.462359</v>
+        <v>20.375582</v>
       </c>
       <c r="O35">
-        <v>4.50171898</v>
+        <v>4.482628040000001</v>
       </c>
       <c r="P35">
-        <v>15.96064002</v>
+        <v>15.89295396</v>
       </c>
       <c r="Q35">
-        <v>16.13464002</v>
+        <v>16.06695396</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.092748136400273</v>
+        <v>0.09334641288507269</v>
       </c>
       <c r="T35">
-        <v>0.683152589188354</v>
+        <v>0.6918582410199149</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.145574113514927</v>
+        <v>7.905998404293901</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07579683250414797</v>
+        <v>0.07568151362011302</v>
       </c>
       <c r="C36">
-        <v>130.5851763673628</v>
+        <v>129.6293264950078</v>
       </c>
       <c r="D36">
-        <v>184.5331763673628</v>
+        <v>185.1993264950079</v>
       </c>
       <c r="E36">
-        <v>28.048</v>
+        <v>29.67</v>
       </c>
       <c r="F36">
-        <v>55.148</v>
+        <v>56.77</v>
       </c>
       <c r="G36">
         <v>1.2</v>
@@ -4227,28 +4227,28 @@
         <v>23.326</v>
       </c>
       <c r="M36">
-        <v>2.950418</v>
+        <v>3.037195</v>
       </c>
       <c r="N36">
-        <v>20.375582</v>
+        <v>20.288805</v>
       </c>
       <c r="O36">
-        <v>4.482628040000001</v>
+        <v>4.4635371</v>
       </c>
       <c r="P36">
-        <v>15.89295396</v>
+        <v>15.8252679</v>
       </c>
       <c r="Q36">
-        <v>16.06695396</v>
+        <v>15.9992679</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09334641288507269</v>
+        <v>0.09396309787709697</v>
       </c>
       <c r="T36">
-        <v>0.6918582410199149</v>
+        <v>0.7008317590616778</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.905998404293901</v>
+        <v>7.680112735599788</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07568151362011302</v>
+        <v>0.07579083473607809</v>
       </c>
       <c r="C37">
-        <v>129.6293264950078</v>
+        <v>127.3757048633139</v>
       </c>
       <c r="D37">
-        <v>185.1993264950079</v>
+        <v>184.5677048633139</v>
       </c>
       <c r="E37">
-        <v>29.67</v>
+        <v>31.292</v>
       </c>
       <c r="F37">
-        <v>56.77</v>
+        <v>58.392</v>
       </c>
       <c r="G37">
         <v>1.2</v>
@@ -4309,45 +4309,45 @@
         <v>23.326</v>
       </c>
       <c r="M37">
-        <v>3.037195</v>
+        <v>3.1706856</v>
       </c>
       <c r="N37">
-        <v>20.288805</v>
+        <v>20.1553144</v>
       </c>
       <c r="O37">
-        <v>4.4635371</v>
+        <v>4.434169168</v>
       </c>
       <c r="P37">
-        <v>15.8252679</v>
+        <v>15.721145232</v>
       </c>
       <c r="Q37">
-        <v>15.9992679</v>
+        <v>15.895145232</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09396309787709697</v>
+        <v>0.09459905427512202</v>
       </c>
       <c r="T37">
-        <v>0.7008317590616778</v>
+        <v>0.7100856995422458</v>
       </c>
       <c r="U37">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V37">
         <v>0.22</v>
       </c>
       <c r="W37">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y37">
-        <v>7.680112735599788</v>
+        <v>7.356768517193884</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07579083473607809</v>
+        <v>0.07568175585204316</v>
       </c>
       <c r="C38">
-        <v>127.3757048633139</v>
+        <v>126.3839221793871</v>
       </c>
       <c r="D38">
-        <v>184.5677048633139</v>
+        <v>185.1979221793871</v>
       </c>
       <c r="E38">
-        <v>31.29199999999999</v>
+        <v>32.91399999999999</v>
       </c>
       <c r="F38">
-        <v>58.392</v>
+        <v>60.014</v>
       </c>
       <c r="G38">
         <v>1.2</v>
@@ -4391,28 +4391,28 @@
         <v>23.326</v>
       </c>
       <c r="M38">
-        <v>3.1706856</v>
+        <v>3.2587602</v>
       </c>
       <c r="N38">
-        <v>20.1553144</v>
+        <v>20.0672398</v>
       </c>
       <c r="O38">
-        <v>4.434169168</v>
+        <v>4.414792756</v>
       </c>
       <c r="P38">
-        <v>15.721145232</v>
+        <v>15.652447044</v>
       </c>
       <c r="Q38">
-        <v>15.895145232</v>
+        <v>15.826447044</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09459905427512202</v>
+        <v>0.09525519976514787</v>
       </c>
       <c r="T38">
-        <v>0.7100856995422457</v>
+        <v>0.7196334159110856</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.356768517193885</v>
+        <v>7.157936935648103</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07568175585204316</v>
+        <v>0.07557267696800821</v>
       </c>
       <c r="C39">
-        <v>126.3839221793871</v>
+        <v>125.3964580698932</v>
       </c>
       <c r="D39">
-        <v>185.1979221793871</v>
+        <v>185.8324580698932</v>
       </c>
       <c r="E39">
-        <v>32.91399999999999</v>
+        <v>34.53599999999999</v>
       </c>
       <c r="F39">
-        <v>60.014</v>
+        <v>61.636</v>
       </c>
       <c r="G39">
         <v>1.2</v>
@@ -4473,28 +4473,28 @@
         <v>23.326</v>
       </c>
       <c r="M39">
-        <v>3.2587602</v>
+        <v>3.3468348</v>
       </c>
       <c r="N39">
-        <v>20.0672398</v>
+        <v>19.9791652</v>
       </c>
       <c r="O39">
-        <v>4.414792756</v>
+        <v>4.395416344</v>
       </c>
       <c r="P39">
-        <v>15.652447044</v>
+        <v>15.583748856</v>
       </c>
       <c r="Q39">
-        <v>15.826447044</v>
+        <v>15.757748856</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09525519976514787</v>
+        <v>0.09593251123872293</v>
       </c>
       <c r="T39">
-        <v>0.7196334159110856</v>
+        <v>0.7294891231305333</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.157936935648103</v>
+        <v>6.96957017418368</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07557267696800821</v>
+        <v>0.07546359808397328</v>
       </c>
       <c r="C40">
-        <v>125.3964580698932</v>
+        <v>124.4133570770979</v>
       </c>
       <c r="D40">
-        <v>185.8324580698932</v>
+        <v>186.4713570770979</v>
       </c>
       <c r="E40">
-        <v>34.53599999999999</v>
+        <v>36.15799999999999</v>
       </c>
       <c r="F40">
-        <v>61.636</v>
+        <v>63.258</v>
       </c>
       <c r="G40">
         <v>1.2</v>
@@ -4555,28 +4555,28 @@
         <v>23.326</v>
       </c>
       <c r="M40">
-        <v>3.3468348</v>
+        <v>3.4349094</v>
       </c>
       <c r="N40">
-        <v>19.9791652</v>
+        <v>19.8910906</v>
       </c>
       <c r="O40">
-        <v>4.395416344</v>
+        <v>4.376039932</v>
       </c>
       <c r="P40">
-        <v>15.583748856</v>
+        <v>15.515050668</v>
       </c>
       <c r="Q40">
-        <v>15.757748856</v>
+        <v>15.689050668</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09593251123872293</v>
+        <v>0.09663202964585783</v>
       </c>
       <c r="T40">
-        <v>0.7294891231305333</v>
+        <v>0.7396679682916022</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.96957017418368</v>
+        <v>6.790863246640509</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07546359808397328</v>
+        <v>0.07535451919993834</v>
       </c>
       <c r="C41">
-        <v>124.4133570770979</v>
+        <v>123.4346643579324</v>
       </c>
       <c r="D41">
-        <v>186.4713570770979</v>
+        <v>187.1146643579324</v>
       </c>
       <c r="E41">
-        <v>36.15799999999999</v>
+        <v>37.77999999999999</v>
       </c>
       <c r="F41">
-        <v>63.258</v>
+        <v>64.88</v>
       </c>
       <c r="G41">
         <v>1.2</v>
@@ -4637,28 +4637,28 @@
         <v>23.326</v>
       </c>
       <c r="M41">
-        <v>3.4349094</v>
+        <v>3.522984</v>
       </c>
       <c r="N41">
-        <v>19.8910906</v>
+        <v>19.803016</v>
       </c>
       <c r="O41">
-        <v>4.376039932</v>
+        <v>4.35666352</v>
       </c>
       <c r="P41">
-        <v>15.515050668</v>
+        <v>15.44635248</v>
       </c>
       <c r="Q41">
-        <v>15.689050668</v>
+        <v>15.62035248</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09663202964585783</v>
+        <v>0.09735486533323057</v>
       </c>
       <c r="T41">
-        <v>0.7396679682916022</v>
+        <v>0.7501861082913733</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.790863246640509</v>
+        <v>6.621091665474496</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07535451919993834</v>
+        <v>0.07524544031590341</v>
       </c>
       <c r="C42">
-        <v>123.4346643579324</v>
+        <v>122.4604256946322</v>
       </c>
       <c r="D42">
-        <v>187.1146643579324</v>
+        <v>187.7624256946322</v>
       </c>
       <c r="E42">
-        <v>37.77999999999999</v>
+        <v>39.40199999999999</v>
       </c>
       <c r="F42">
-        <v>64.88</v>
+        <v>66.502</v>
       </c>
       <c r="G42">
         <v>1.2</v>
@@ -4719,28 +4719,28 @@
         <v>23.326</v>
       </c>
       <c r="M42">
-        <v>3.522984</v>
+        <v>3.6110586</v>
       </c>
       <c r="N42">
-        <v>19.803016</v>
+        <v>19.7149414</v>
       </c>
       <c r="O42">
-        <v>4.35666352</v>
+        <v>4.337287108</v>
       </c>
       <c r="P42">
-        <v>15.44635248</v>
+        <v>15.377654292</v>
       </c>
       <c r="Q42">
-        <v>15.62035248</v>
+        <v>15.551654292</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09735486533323057</v>
+        <v>0.09810220392526001</v>
       </c>
       <c r="T42">
-        <v>0.7501861082913733</v>
+        <v>0.7610607954097809</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.621091665474496</v>
+        <v>6.459601624853167</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07524544031590341</v>
+        <v>0.07513636143186846</v>
       </c>
       <c r="C43">
-        <v>122.4604256946322</v>
+        <v>121.4906875055989</v>
       </c>
       <c r="D43">
-        <v>187.7624256946322</v>
+        <v>188.4146875055989</v>
       </c>
       <c r="E43">
-        <v>39.40199999999999</v>
+        <v>41.02399999999999</v>
       </c>
       <c r="F43">
-        <v>66.502</v>
+        <v>68.124</v>
       </c>
       <c r="G43">
         <v>1.2</v>
@@ -4801,28 +4801,28 @@
         <v>23.326</v>
       </c>
       <c r="M43">
-        <v>3.6110586</v>
+        <v>3.6991332</v>
       </c>
       <c r="N43">
-        <v>19.7149414</v>
+        <v>19.6268668</v>
       </c>
       <c r="O43">
-        <v>4.337287108</v>
+        <v>4.317910696</v>
       </c>
       <c r="P43">
-        <v>15.377654292</v>
+        <v>15.308956104</v>
       </c>
       <c r="Q43">
-        <v>15.551654292</v>
+        <v>15.482956104</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09810220392526001</v>
+        <v>0.0988753128135663</v>
       </c>
       <c r="T43">
-        <v>0.7610607954097809</v>
+        <v>0.7723104717391679</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.459601624853167</v>
+        <v>6.305801586166186</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07513636143186847</v>
+        <v>0.07502728254783353</v>
       </c>
       <c r="C44">
-        <v>121.4906875055988</v>
+        <v>120.5254968564875</v>
       </c>
       <c r="D44">
-        <v>188.4146875055988</v>
+        <v>189.0714968564875</v>
       </c>
       <c r="E44">
-        <v>41.02399999999999</v>
+        <v>42.64599999999999</v>
       </c>
       <c r="F44">
-        <v>68.124</v>
+        <v>69.746</v>
       </c>
       <c r="G44">
         <v>1.2</v>
@@ -4883,28 +4883,28 @@
         <v>23.326</v>
       </c>
       <c r="M44">
-        <v>3.6991332</v>
+        <v>3.7872078</v>
       </c>
       <c r="N44">
-        <v>19.6268668</v>
+        <v>19.5387922</v>
       </c>
       <c r="O44">
-        <v>4.317910696</v>
+        <v>4.298534284</v>
       </c>
       <c r="P44">
-        <v>15.308956104</v>
+        <v>15.240257916</v>
       </c>
       <c r="Q44">
-        <v>15.482956104</v>
+        <v>15.414257916</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0988753128135663</v>
+        <v>0.09967554832953249</v>
       </c>
       <c r="T44">
-        <v>0.7723104717391679</v>
+        <v>0.7839548735537967</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.305801586166186</v>
+        <v>6.159155037650693</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07502728254783353</v>
+        <v>0.0752614036637986</v>
       </c>
       <c r="C45">
-        <v>120.5254968564875</v>
+        <v>117.4993478765826</v>
       </c>
       <c r="D45">
-        <v>189.0714968564875</v>
+        <v>187.6673478765826</v>
       </c>
       <c r="E45">
-        <v>42.64599999999999</v>
+        <v>44.26799999999999</v>
       </c>
       <c r="F45">
-        <v>69.746</v>
+        <v>71.36799999999999</v>
       </c>
       <c r="G45">
         <v>1.2</v>
@@ -4965,45 +4965,45 @@
         <v>23.326</v>
       </c>
       <c r="M45">
-        <v>3.7872078</v>
+        <v>3.9466504</v>
       </c>
       <c r="N45">
-        <v>19.5387922</v>
+        <v>19.3793496</v>
       </c>
       <c r="O45">
-        <v>4.298534284</v>
+        <v>4.263456912000001</v>
       </c>
       <c r="P45">
-        <v>15.240257916</v>
+        <v>15.115892688</v>
       </c>
       <c r="Q45">
-        <v>15.414257916</v>
+        <v>15.289892688</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09967554832953249</v>
+        <v>0.1005043636853546</v>
       </c>
       <c r="T45">
-        <v>0.7839548735537967</v>
+        <v>0.7960151468618051</v>
       </c>
       <c r="U45">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.22</v>
       </c>
       <c r="W45">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>6.159155037650693</v>
+        <v>5.910328414191437</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0752614036637986</v>
+        <v>0.07516012477976365</v>
       </c>
       <c r="C46">
-        <v>117.4993478765826</v>
+        <v>116.4822034034776</v>
       </c>
       <c r="D46">
-        <v>187.6673478765826</v>
+        <v>188.2722034034776</v>
       </c>
       <c r="E46">
-        <v>44.26799999999999</v>
+        <v>45.88999999999999</v>
       </c>
       <c r="F46">
-        <v>71.36799999999999</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="G46">
         <v>1.2</v>
@@ -5047,28 +5047,28 @@
         <v>23.326</v>
       </c>
       <c r="M46">
-        <v>3.9466504</v>
+        <v>4.036347</v>
       </c>
       <c r="N46">
-        <v>19.3793496</v>
+        <v>19.289653</v>
       </c>
       <c r="O46">
-        <v>4.263456912000001</v>
+        <v>4.243723660000001</v>
       </c>
       <c r="P46">
-        <v>15.115892688</v>
+        <v>15.04592934</v>
       </c>
       <c r="Q46">
-        <v>15.289892688</v>
+        <v>15.21992934</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1005043636853546</v>
+        <v>0.1013633177813884</v>
       </c>
       <c r="T46">
-        <v>0.7960151468618051</v>
+        <v>0.8085139755628318</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.910328414191437</v>
+        <v>5.77898778276496</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07516012477976365</v>
+        <v>0.07505884589572871</v>
       </c>
       <c r="C47">
-        <v>116.4822034034776</v>
+        <v>115.4689704596569</v>
       </c>
       <c r="D47">
-        <v>188.2722034034776</v>
+        <v>188.8809704596569</v>
       </c>
       <c r="E47">
-        <v>45.88999999999999</v>
+        <v>47.51199999999999</v>
       </c>
       <c r="F47">
-        <v>72.98999999999999</v>
+        <v>74.61199999999999</v>
       </c>
       <c r="G47">
         <v>1.2</v>
@@ -5129,28 +5129,28 @@
         <v>23.326</v>
       </c>
       <c r="M47">
-        <v>4.036347</v>
+        <v>4.1260436</v>
       </c>
       <c r="N47">
-        <v>19.289653</v>
+        <v>19.1999564</v>
       </c>
       <c r="O47">
-        <v>4.243723660000001</v>
+        <v>4.223990408000001</v>
       </c>
       <c r="P47">
-        <v>15.04592934</v>
+        <v>14.975965992</v>
       </c>
       <c r="Q47">
-        <v>15.21992934</v>
+        <v>15.149965992</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1013633177813884</v>
+        <v>0.1022540849920902</v>
       </c>
       <c r="T47">
-        <v>0.8085139755628318</v>
+        <v>0.8214757238453781</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.77898778276496</v>
+        <v>5.653357613574419</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07505884589572871</v>
+        <v>0.07495756701169377</v>
       </c>
       <c r="C48">
-        <v>115.4689704596569</v>
+        <v>114.4596871113025</v>
       </c>
       <c r="D48">
-        <v>188.8809704596569</v>
+        <v>189.4936871113025</v>
       </c>
       <c r="E48">
-        <v>47.51199999999999</v>
+        <v>49.13399999999999</v>
       </c>
       <c r="F48">
-        <v>74.61199999999999</v>
+        <v>76.23399999999999</v>
       </c>
       <c r="G48">
         <v>1.2</v>
@@ -5211,28 +5211,28 @@
         <v>23.326</v>
       </c>
       <c r="M48">
-        <v>4.1260436</v>
+        <v>4.2157402</v>
       </c>
       <c r="N48">
-        <v>19.1999564</v>
+        <v>19.1102598</v>
       </c>
       <c r="O48">
-        <v>4.223990408000001</v>
+        <v>4.204257156000001</v>
       </c>
       <c r="P48">
-        <v>14.975965992</v>
+        <v>14.906002644</v>
       </c>
       <c r="Q48">
-        <v>15.149965992</v>
+        <v>15.080002644</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1022540849920902</v>
+        <v>0.1031784660597996</v>
       </c>
       <c r="T48">
-        <v>0.8214757238453781</v>
+        <v>0.8349265947046244</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.653357613574419</v>
+        <v>5.533073409030282</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07495756701169377</v>
+        <v>0.07485628812765885</v>
       </c>
       <c r="C49">
-        <v>114.4596871113025</v>
+        <v>113.4543919201397</v>
       </c>
       <c r="D49">
-        <v>189.4936871113025</v>
+        <v>190.1103919201397</v>
       </c>
       <c r="E49">
-        <v>49.13399999999999</v>
+        <v>50.75599999999999</v>
       </c>
       <c r="F49">
-        <v>76.23399999999999</v>
+        <v>77.85599999999999</v>
       </c>
       <c r="G49">
         <v>1.2</v>
@@ -5293,28 +5293,28 @@
         <v>23.326</v>
       </c>
       <c r="M49">
-        <v>4.2157402</v>
+        <v>4.3054368</v>
       </c>
       <c r="N49">
-        <v>19.1102598</v>
+        <v>19.0205632</v>
       </c>
       <c r="O49">
-        <v>4.204257156000001</v>
+        <v>4.184523904000001</v>
       </c>
       <c r="P49">
-        <v>14.906002644</v>
+        <v>14.836039296</v>
       </c>
       <c r="Q49">
-        <v>15.080002644</v>
+        <v>15.010039296</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1031784660597996</v>
+        <v>0.1041384002454978</v>
       </c>
       <c r="T49">
-        <v>0.8349265947046244</v>
+        <v>0.8488948067507647</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.533073409030282</v>
+        <v>5.417801046342151</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07485628812765883</v>
+        <v>0.0747550092436239</v>
       </c>
       <c r="C50">
-        <v>113.4543919201398</v>
+        <v>112.4531239515281</v>
       </c>
       <c r="D50">
-        <v>190.1103919201398</v>
+        <v>190.7311239515281</v>
       </c>
       <c r="E50">
-        <v>50.75599999999999</v>
+        <v>52.37799999999999</v>
       </c>
       <c r="F50">
-        <v>77.85599999999999</v>
+        <v>79.47799999999999</v>
       </c>
       <c r="G50">
         <v>1.2</v>
@@ -5375,28 +5375,28 @@
         <v>23.326</v>
       </c>
       <c r="M50">
-        <v>4.3054368</v>
+        <v>4.3951334</v>
       </c>
       <c r="N50">
-        <v>19.0205632</v>
+        <v>18.9308666</v>
       </c>
       <c r="O50">
-        <v>4.184523904000001</v>
+        <v>4.164790652000001</v>
       </c>
       <c r="P50">
-        <v>14.836039296</v>
+        <v>14.766075948</v>
       </c>
       <c r="Q50">
-        <v>15.010039296</v>
+        <v>14.940075948</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1041384002454977</v>
+        <v>0.1051359789090665</v>
       </c>
       <c r="T50">
-        <v>0.8488948067507646</v>
+        <v>0.8634107918183221</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.417801046342151</v>
+        <v>5.307233678049454</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0747550092436239</v>
+        <v>0.07465373035958894</v>
       </c>
       <c r="C51">
-        <v>112.4531239515281</v>
+        <v>111.4559227827093</v>
       </c>
       <c r="D51">
-        <v>190.7311239515281</v>
+        <v>191.3559227827093</v>
       </c>
       <c r="E51">
-        <v>52.37799999999999</v>
+        <v>53.99999999999999</v>
       </c>
       <c r="F51">
-        <v>79.47799999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G51">
         <v>1.2</v>
@@ -5457,28 +5457,28 @@
         <v>23.326</v>
       </c>
       <c r="M51">
-        <v>4.3951334</v>
+        <v>4.48483</v>
       </c>
       <c r="N51">
-        <v>18.9308666</v>
+        <v>18.84117</v>
       </c>
       <c r="O51">
-        <v>4.164790652000001</v>
+        <v>4.145057400000001</v>
       </c>
       <c r="P51">
-        <v>14.766075948</v>
+        <v>14.6961126</v>
       </c>
       <c r="Q51">
-        <v>14.940075948</v>
+        <v>14.8701126</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1051359789090665</v>
+        <v>0.1061734607191779</v>
       </c>
       <c r="T51">
-        <v>0.8634107918183221</v>
+        <v>0.878507416288582</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.307233678049454</v>
+        <v>5.201089004488465</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07465373035958894</v>
+        <v>0.074552451475554</v>
       </c>
       <c r="C52">
-        <v>111.4559227827093</v>
+        <v>110.4628285112196</v>
       </c>
       <c r="D52">
-        <v>191.3559227827093</v>
+        <v>191.9848285112196</v>
       </c>
       <c r="E52">
-        <v>53.99999999999999</v>
+        <v>55.62199999999999</v>
       </c>
       <c r="F52">
-        <v>81.09999999999999</v>
+        <v>82.72199999999999</v>
       </c>
       <c r="G52">
         <v>1.2</v>
@@ -5539,28 +5539,28 @@
         <v>23.326</v>
       </c>
       <c r="M52">
-        <v>4.48483</v>
+        <v>4.5745266</v>
       </c>
       <c r="N52">
-        <v>18.84117</v>
+        <v>18.7514734</v>
       </c>
       <c r="O52">
-        <v>4.145057400000001</v>
+        <v>4.125324148000001</v>
       </c>
       <c r="P52">
-        <v>14.6961126</v>
+        <v>14.626149252</v>
       </c>
       <c r="Q52">
-        <v>14.8701126</v>
+        <v>14.800149252</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1061734607191779</v>
+        <v>0.1072532887256204</v>
       </c>
       <c r="T52">
-        <v>0.878507416288582</v>
+        <v>0.8942202295127301</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.201089004488465</v>
+        <v>5.099106867145554</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.074552451475554</v>
+        <v>0.07445117259151908</v>
       </c>
       <c r="C53">
-        <v>110.4628285112196</v>
+        <v>109.4738817634678</v>
       </c>
       <c r="D53">
-        <v>191.9848285112196</v>
+        <v>192.6178817634678</v>
       </c>
       <c r="E53">
-        <v>55.62199999999999</v>
+        <v>57.24399999999999</v>
       </c>
       <c r="F53">
-        <v>82.72199999999999</v>
+        <v>84.34399999999999</v>
       </c>
       <c r="G53">
         <v>1.2</v>
@@ -5621,28 +5621,28 @@
         <v>23.326</v>
       </c>
       <c r="M53">
-        <v>4.5745266</v>
+        <v>4.664223199999999</v>
       </c>
       <c r="N53">
-        <v>18.7514734</v>
+        <v>18.6617768</v>
       </c>
       <c r="O53">
-        <v>4.125324148000001</v>
+        <v>4.105590896000001</v>
       </c>
       <c r="P53">
-        <v>14.626149252</v>
+        <v>14.556185904</v>
       </c>
       <c r="Q53">
-        <v>14.800149252</v>
+        <v>14.730185904</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1072532887256204</v>
+        <v>0.1083781095656647</v>
       </c>
       <c r="T53">
-        <v>0.8942202295127301</v>
+        <v>0.9105877432878842</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.099106867145554</v>
+        <v>5.001047119700448</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07445117259151908</v>
+        <v>0.07434989370748413</v>
       </c>
       <c r="C54">
-        <v>109.4738817634678</v>
+        <v>108.4891237034839</v>
       </c>
       <c r="D54">
-        <v>192.6178817634678</v>
+        <v>193.2551237034839</v>
       </c>
       <c r="E54">
-        <v>57.24399999999999</v>
+        <v>58.86599999999999</v>
       </c>
       <c r="F54">
-        <v>84.34399999999999</v>
+        <v>85.96599999999999</v>
       </c>
       <c r="G54">
         <v>1.2</v>
@@ -5703,28 +5703,28 @@
         <v>23.326</v>
       </c>
       <c r="M54">
-        <v>4.664223199999999</v>
+        <v>4.7539198</v>
       </c>
       <c r="N54">
-        <v>18.6617768</v>
+        <v>18.5720802</v>
       </c>
       <c r="O54">
-        <v>4.105590896000001</v>
+        <v>4.085857644000001</v>
       </c>
       <c r="P54">
-        <v>14.556185904</v>
+        <v>14.486222556</v>
       </c>
       <c r="Q54">
-        <v>14.730185904</v>
+        <v>14.660222556</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1083781095656647</v>
+        <v>0.1095507951223067</v>
       </c>
       <c r="T54">
-        <v>0.9105877432878842</v>
+        <v>0.9276517470109172</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.001047119700448</v>
+        <v>4.906687740083457</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07434989370748413</v>
+        <v>0.07424861482344919</v>
       </c>
       <c r="C55">
-        <v>108.4891237034839</v>
+        <v>107.508596041841</v>
       </c>
       <c r="D55">
-        <v>193.2551237034839</v>
+        <v>193.896596041841</v>
       </c>
       <c r="E55">
-        <v>58.86599999999999</v>
+        <v>60.48799999999999</v>
       </c>
       <c r="F55">
-        <v>85.96599999999999</v>
+        <v>87.58799999999999</v>
       </c>
       <c r="G55">
         <v>1.2</v>
@@ -5785,28 +5785,28 @@
         <v>23.326</v>
       </c>
       <c r="M55">
-        <v>4.7539198</v>
+        <v>4.8436164</v>
       </c>
       <c r="N55">
-        <v>18.5720802</v>
+        <v>18.4823836</v>
       </c>
       <c r="O55">
-        <v>4.085857644000001</v>
+        <v>4.066124392</v>
       </c>
       <c r="P55">
-        <v>14.486222556</v>
+        <v>14.416259208</v>
       </c>
       <c r="Q55">
-        <v>14.660222556</v>
+        <v>14.590259208</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1095507951223067</v>
+        <v>0.1107744670074982</v>
       </c>
       <c r="T55">
-        <v>0.9276517470109172</v>
+        <v>0.9454576639392995</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.906687740083457</v>
+        <v>4.815823152304134</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07424861482344919</v>
+        <v>0.07414733593941426</v>
       </c>
       <c r="C56">
-        <v>107.508596041841</v>
+        <v>106.532341044757</v>
       </c>
       <c r="D56">
-        <v>193.896596041841</v>
+        <v>194.542341044757</v>
       </c>
       <c r="E56">
-        <v>60.48799999999999</v>
+        <v>62.11000000000001</v>
       </c>
       <c r="F56">
-        <v>87.58799999999999</v>
+        <v>89.21000000000001</v>
       </c>
       <c r="G56">
         <v>1.2</v>
@@ -5867,28 +5867,28 @@
         <v>23.326</v>
       </c>
       <c r="M56">
-        <v>4.8436164</v>
+        <v>4.933313000000001</v>
       </c>
       <c r="N56">
-        <v>18.4823836</v>
+        <v>18.392687</v>
       </c>
       <c r="O56">
-        <v>4.066124392</v>
+        <v>4.04639114</v>
       </c>
       <c r="P56">
-        <v>14.416259208</v>
+        <v>14.34629586</v>
       </c>
       <c r="Q56">
-        <v>14.590259208</v>
+        <v>14.52029586</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1107744670074982</v>
+        <v>0.1120525243098095</v>
       </c>
       <c r="T56">
-        <v>0.9454576639392995</v>
+        <v>0.9640549549533878</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.815823152304134</v>
+        <v>4.728262731353149</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07414733593941426</v>
+        <v>0.07404605705537932</v>
       </c>
       <c r="C57">
-        <v>106.532341044757</v>
+        <v>105.5604015433777</v>
       </c>
       <c r="D57">
-        <v>194.542341044757</v>
+        <v>195.1924015433777</v>
       </c>
       <c r="E57">
-        <v>62.11000000000001</v>
+        <v>63.73200000000001</v>
       </c>
       <c r="F57">
-        <v>89.21000000000001</v>
+        <v>90.83200000000001</v>
       </c>
       <c r="G57">
         <v>1.2</v>
@@ -5949,28 +5949,28 @@
         <v>23.326</v>
       </c>
       <c r="M57">
-        <v>4.933313000000001</v>
+        <v>5.023009600000001</v>
       </c>
       <c r="N57">
-        <v>18.392687</v>
+        <v>18.3029904</v>
       </c>
       <c r="O57">
-        <v>4.04639114</v>
+        <v>4.026657888</v>
       </c>
       <c r="P57">
-        <v>14.34629586</v>
+        <v>14.276332512</v>
       </c>
       <c r="Q57">
-        <v>14.52029586</v>
+        <v>14.450332512</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1120525243098095</v>
+        <v>0.1133886751258621</v>
       </c>
       <c r="T57">
-        <v>0.9640549549533878</v>
+        <v>0.9834975773772072</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.728262731353149</v>
+        <v>4.643829468293271</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07404605705537932</v>
+        <v>0.07394477817134437</v>
       </c>
       <c r="C58">
-        <v>105.5604015433777</v>
+        <v>104.5928209432469</v>
       </c>
       <c r="D58">
-        <v>195.1924015433777</v>
+        <v>195.846820943247</v>
       </c>
       <c r="E58">
-        <v>63.73200000000001</v>
+        <v>65.35400000000001</v>
       </c>
       <c r="F58">
-        <v>90.83200000000001</v>
+        <v>92.45400000000001</v>
       </c>
       <c r="G58">
         <v>1.2</v>
@@ -6031,28 +6031,28 @@
         <v>23.326</v>
       </c>
       <c r="M58">
-        <v>5.023009600000001</v>
+        <v>5.112706200000001</v>
       </c>
       <c r="N58">
-        <v>18.3029904</v>
+        <v>18.2132938</v>
       </c>
       <c r="O58">
-        <v>4.026657888</v>
+        <v>4.006924636</v>
       </c>
       <c r="P58">
-        <v>14.276332512</v>
+        <v>14.206369164</v>
       </c>
       <c r="Q58">
-        <v>14.450332512</v>
+        <v>14.380369164</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1133886751258621</v>
+        <v>0.1147869724914986</v>
       </c>
       <c r="T58">
-        <v>0.9834975773772072</v>
+        <v>1.003844507820739</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.643829468293271</v>
+        <v>4.562358775867073</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07394477817134437</v>
+        <v>0.07497449928730944</v>
       </c>
       <c r="C59">
-        <v>104.5928209432469</v>
+        <v>96.51497369451674</v>
       </c>
       <c r="D59">
-        <v>195.846820943247</v>
+        <v>189.3909736945168</v>
       </c>
       <c r="E59">
-        <v>65.35400000000001</v>
+        <v>66.976</v>
       </c>
       <c r="F59">
-        <v>92.45400000000001</v>
+        <v>94.07600000000001</v>
       </c>
       <c r="G59">
         <v>1.2</v>
@@ -6113,45 +6113,45 @@
         <v>23.326</v>
       </c>
       <c r="M59">
-        <v>5.112706200000001</v>
+        <v>5.437592800000001</v>
       </c>
       <c r="N59">
-        <v>18.2132938</v>
+        <v>17.8884072</v>
       </c>
       <c r="O59">
-        <v>4.006924636</v>
+        <v>3.935449584</v>
       </c>
       <c r="P59">
-        <v>14.206369164</v>
+        <v>13.952957616</v>
       </c>
       <c r="Q59">
-        <v>14.380369164</v>
+        <v>14.126957616</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1147869724914986</v>
+        <v>0.1162518554459749</v>
       </c>
       <c r="T59">
-        <v>1.003844507820739</v>
+        <v>1.025160339713963</v>
       </c>
       <c r="U59">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V59">
         <v>0.22</v>
       </c>
       <c r="W59">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>4.562358775867073</v>
+        <v>4.289765868455614</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07497449928730943</v>
+        <v>0.07489272040327449</v>
       </c>
       <c r="C60">
-        <v>96.51497369451681</v>
+        <v>95.39008770319474</v>
       </c>
       <c r="D60">
-        <v>189.3909736945168</v>
+        <v>189.8880877031947</v>
       </c>
       <c r="E60">
-        <v>66.976</v>
+        <v>68.59799999999998</v>
       </c>
       <c r="F60">
-        <v>94.07599999999999</v>
+        <v>95.69799999999999</v>
       </c>
       <c r="G60">
         <v>1.2</v>
@@ -6195,28 +6195,28 @@
         <v>23.326</v>
       </c>
       <c r="M60">
-        <v>5.4375928</v>
+        <v>5.5313444</v>
       </c>
       <c r="N60">
-        <v>17.8884072</v>
+        <v>17.7946556</v>
       </c>
       <c r="O60">
-        <v>3.935449584</v>
+        <v>3.914824232</v>
       </c>
       <c r="P60">
-        <v>13.952957616</v>
+        <v>13.879831368</v>
       </c>
       <c r="Q60">
-        <v>14.126957616</v>
+        <v>14.053831368</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1162518554459748</v>
+        <v>0.1177881961055476</v>
       </c>
       <c r="T60">
-        <v>1.025160339713963</v>
+        <v>1.047515968284905</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.289765868455615</v>
+        <v>4.217057972380096</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07489272040327449</v>
+        <v>0.07481094151923956</v>
       </c>
       <c r="C61">
-        <v>95.39008770319474</v>
+        <v>94.26781823247356</v>
       </c>
       <c r="D61">
-        <v>189.8880877031947</v>
+        <v>190.3878182324736</v>
       </c>
       <c r="E61">
-        <v>68.59799999999998</v>
+        <v>70.22</v>
       </c>
       <c r="F61">
-        <v>95.69799999999999</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="G61">
         <v>1.2</v>
@@ -6277,28 +6277,28 @@
         <v>23.326</v>
       </c>
       <c r="M61">
-        <v>5.5313444</v>
+        <v>5.625096</v>
       </c>
       <c r="N61">
-        <v>17.7946556</v>
+        <v>17.700904</v>
       </c>
       <c r="O61">
-        <v>3.914824232</v>
+        <v>3.89419888</v>
       </c>
       <c r="P61">
-        <v>13.879831368</v>
+        <v>13.80670512</v>
       </c>
       <c r="Q61">
-        <v>14.053831368</v>
+        <v>13.98070512</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1177881961055476</v>
+        <v>0.1194013537980989</v>
       </c>
       <c r="T61">
-        <v>1.047515968284905</v>
+        <v>1.070989378284395</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.217057972380096</v>
+        <v>4.146773672840428</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07481094151923956</v>
+        <v>0.07472916263520463</v>
       </c>
       <c r="C62">
-        <v>94.26781823247356</v>
+        <v>93.1481859946385</v>
       </c>
       <c r="D62">
-        <v>190.3878182324736</v>
+        <v>190.8901859946385</v>
       </c>
       <c r="E62">
-        <v>70.22</v>
+        <v>71.84199999999998</v>
       </c>
       <c r="F62">
-        <v>97.31999999999999</v>
+        <v>98.94199999999999</v>
       </c>
       <c r="G62">
         <v>1.2</v>
@@ -6359,28 +6359,28 @@
         <v>23.326</v>
       </c>
       <c r="M62">
-        <v>5.625096</v>
+        <v>5.7188476</v>
       </c>
       <c r="N62">
-        <v>17.700904</v>
+        <v>17.6071524</v>
       </c>
       <c r="O62">
-        <v>3.89419888</v>
+        <v>3.873573528</v>
       </c>
       <c r="P62">
-        <v>13.80670512</v>
+        <v>13.733578872</v>
       </c>
       <c r="Q62">
-        <v>13.98070512</v>
+        <v>13.907578872</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1194013537980989</v>
+        <v>0.1210972375261657</v>
       </c>
       <c r="T62">
-        <v>1.070989378284395</v>
+        <v>1.095666552899243</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.146773672840428</v>
+        <v>4.078793776564355</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07472916263520463</v>
+        <v>0.07464738375116969</v>
       </c>
       <c r="C63">
-        <v>93.1481859946385</v>
+        <v>92.03121192116342</v>
       </c>
       <c r="D63">
-        <v>190.8901859946385</v>
+        <v>191.3952119211634</v>
       </c>
       <c r="E63">
-        <v>71.84199999999998</v>
+        <v>73.464</v>
       </c>
       <c r="F63">
-        <v>98.94199999999999</v>
+        <v>100.564</v>
       </c>
       <c r="G63">
         <v>1.2</v>
@@ -6441,28 +6441,28 @@
         <v>23.326</v>
       </c>
       <c r="M63">
-        <v>5.7188476</v>
+        <v>5.8125992</v>
       </c>
       <c r="N63">
-        <v>17.6071524</v>
+        <v>17.5134008</v>
       </c>
       <c r="O63">
-        <v>3.873573528</v>
+        <v>3.852948176</v>
       </c>
       <c r="P63">
-        <v>13.733578872</v>
+        <v>13.660452624</v>
       </c>
       <c r="Q63">
-        <v>13.907578872</v>
+        <v>13.834452624</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1210972375261657</v>
+        <v>0.1228823782925518</v>
       </c>
       <c r="T63">
-        <v>1.095666552899243</v>
+        <v>1.12164252617803</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.078793776564355</v>
+        <v>4.013006780168156</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07464738375116969</v>
+        <v>0.07628550486713476</v>
       </c>
       <c r="C64">
-        <v>92.03121192116342</v>
+        <v>80.77669764382243</v>
       </c>
       <c r="D64">
-        <v>191.3952119211634</v>
+        <v>181.7626976438224</v>
       </c>
       <c r="E64">
-        <v>73.464</v>
+        <v>75.08599999999998</v>
       </c>
       <c r="F64">
-        <v>100.564</v>
+        <v>102.186</v>
       </c>
       <c r="G64">
         <v>1.2</v>
@@ -6523,45 +6523,45 @@
         <v>23.326</v>
       </c>
       <c r="M64">
-        <v>5.8125992</v>
+        <v>6.2640018</v>
       </c>
       <c r="N64">
-        <v>17.5134008</v>
+        <v>17.0619982</v>
       </c>
       <c r="O64">
-        <v>3.852948176</v>
+        <v>3.753639604</v>
       </c>
       <c r="P64">
-        <v>13.660452624</v>
+        <v>13.308358596</v>
       </c>
       <c r="Q64">
-        <v>13.834452624</v>
+        <v>13.482358596</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1228823782925518</v>
+        <v>0.1247640131544182</v>
       </c>
       <c r="T64">
-        <v>1.12164252617803</v>
+        <v>1.149022606120535</v>
       </c>
       <c r="U64">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V64">
         <v>0.22</v>
       </c>
       <c r="W64">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.013006780168156</v>
+        <v>3.723817576169917</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07628550486713476</v>
+        <v>0.0762310259830998</v>
       </c>
       <c r="C65">
-        <v>80.77669764382243</v>
+        <v>79.45943314800837</v>
       </c>
       <c r="D65">
-        <v>181.7626976438224</v>
+        <v>182.0674331480084</v>
       </c>
       <c r="E65">
-        <v>75.08599999999998</v>
+        <v>76.708</v>
       </c>
       <c r="F65">
-        <v>102.186</v>
+        <v>103.808</v>
       </c>
       <c r="G65">
         <v>1.2</v>
@@ -6605,28 +6605,28 @@
         <v>23.326</v>
       </c>
       <c r="M65">
-        <v>6.2640018</v>
+        <v>6.363430399999999</v>
       </c>
       <c r="N65">
-        <v>17.0619982</v>
+        <v>16.9625696</v>
       </c>
       <c r="O65">
-        <v>3.753639604</v>
+        <v>3.731765312</v>
       </c>
       <c r="P65">
-        <v>13.308358596</v>
+        <v>13.230804288</v>
       </c>
       <c r="Q65">
-        <v>13.482358596</v>
+        <v>13.404804288</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1247640131544182</v>
+        <v>0.1267501832863883</v>
       </c>
       <c r="T65">
-        <v>1.149022606120535</v>
+        <v>1.177923801615402</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.723817576169917</v>
+        <v>3.665632926542263</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0762310259830998</v>
+        <v>0.07617654709906488</v>
       </c>
       <c r="C66">
-        <v>79.45943314800837</v>
+        <v>78.14319218102055</v>
       </c>
       <c r="D66">
-        <v>182.0674331480084</v>
+        <v>182.3731921810206</v>
       </c>
       <c r="E66">
-        <v>76.708</v>
+        <v>78.32999999999998</v>
       </c>
       <c r="F66">
-        <v>103.808</v>
+        <v>105.43</v>
       </c>
       <c r="G66">
         <v>1.2</v>
@@ -6687,28 +6687,28 @@
         <v>23.326</v>
       </c>
       <c r="M66">
-        <v>6.363430399999999</v>
+        <v>6.462859</v>
       </c>
       <c r="N66">
-        <v>16.9625696</v>
+        <v>16.863141</v>
       </c>
       <c r="O66">
-        <v>3.731765312</v>
+        <v>3.70989102</v>
       </c>
       <c r="P66">
-        <v>13.230804288</v>
+        <v>13.15324998</v>
       </c>
       <c r="Q66">
-        <v>13.404804288</v>
+        <v>13.32724998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1267501832863883</v>
+        <v>0.1288498488544711</v>
       </c>
       <c r="T66">
-        <v>1.177923801615402</v>
+        <v>1.20847649399569</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.665632926542263</v>
+        <v>3.609238573826227</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07617654709906488</v>
+        <v>0.07612206821502993</v>
       </c>
       <c r="C67">
-        <v>78.14319218102055</v>
+        <v>76.82797990819213</v>
       </c>
       <c r="D67">
-        <v>182.3731921810206</v>
+        <v>182.6799799081921</v>
       </c>
       <c r="E67">
-        <v>78.32999999999998</v>
+        <v>79.952</v>
       </c>
       <c r="F67">
-        <v>105.43</v>
+        <v>107.052</v>
       </c>
       <c r="G67">
         <v>1.2</v>
@@ -6769,28 +6769,28 @@
         <v>23.326</v>
       </c>
       <c r="M67">
-        <v>6.462859</v>
+        <v>6.562287599999999</v>
       </c>
       <c r="N67">
-        <v>16.863141</v>
+        <v>16.7637124</v>
       </c>
       <c r="O67">
-        <v>3.70989102</v>
+        <v>3.688016728</v>
       </c>
       <c r="P67">
-        <v>13.15324998</v>
+        <v>13.075695672</v>
       </c>
       <c r="Q67">
-        <v>13.32724998</v>
+        <v>13.249695672</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1288498488544711</v>
+        <v>0.1310730241618527</v>
       </c>
       <c r="T67">
-        <v>1.20847649399569</v>
+        <v>1.240826403574818</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.609238573826227</v>
+        <v>3.554553140889467</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07612206821502993</v>
+        <v>0.07606758933099499</v>
       </c>
       <c r="C68">
-        <v>76.82797990819213</v>
+        <v>75.51380152967077</v>
       </c>
       <c r="D68">
-        <v>182.6799799081921</v>
+        <v>182.9878015296708</v>
       </c>
       <c r="E68">
-        <v>79.952</v>
+        <v>81.57399999999998</v>
       </c>
       <c r="F68">
-        <v>107.052</v>
+        <v>108.674</v>
       </c>
       <c r="G68">
         <v>1.2</v>
@@ -6851,28 +6851,28 @@
         <v>23.326</v>
       </c>
       <c r="M68">
-        <v>6.562287599999999</v>
+        <v>6.6617162</v>
       </c>
       <c r="N68">
-        <v>16.7637124</v>
+        <v>16.6642838</v>
       </c>
       <c r="O68">
-        <v>3.688016728</v>
+        <v>3.666142436</v>
       </c>
       <c r="P68">
-        <v>13.075695672</v>
+        <v>12.998141364</v>
       </c>
       <c r="Q68">
-        <v>13.249695672</v>
+        <v>13.172141364</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1310730241618527</v>
+        <v>0.1334309373666515</v>
       </c>
       <c r="T68">
-        <v>1.240826403574818</v>
+        <v>1.2751369137345</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.554553140889467</v>
+        <v>3.501500108935892</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07606758933099499</v>
+        <v>0.07749823044696005</v>
       </c>
       <c r="C69">
-        <v>75.51380152967077</v>
+        <v>66.13775447810751</v>
       </c>
       <c r="D69">
-        <v>182.9878015296708</v>
+        <v>175.2337544781075</v>
       </c>
       <c r="E69">
-        <v>81.57399999999998</v>
+        <v>83.196</v>
       </c>
       <c r="F69">
-        <v>108.674</v>
+        <v>110.296</v>
       </c>
       <c r="G69">
         <v>1.2</v>
@@ -6933,45 +6933,45 @@
         <v>23.326</v>
       </c>
       <c r="M69">
-        <v>6.6617162</v>
+        <v>7.069973600000001</v>
       </c>
       <c r="N69">
-        <v>16.6642838</v>
+        <v>16.2560264</v>
       </c>
       <c r="O69">
-        <v>3.666142436</v>
+        <v>3.576325808</v>
       </c>
       <c r="P69">
-        <v>12.998141364</v>
+        <v>12.679700592</v>
       </c>
       <c r="Q69">
-        <v>13.172141364</v>
+        <v>12.853700592</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1334309373666515</v>
+        <v>0.1359362201467502</v>
       </c>
       <c r="T69">
-        <v>1.2751369137345</v>
+        <v>1.311591830779161</v>
       </c>
       <c r="U69">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V69">
         <v>0.22</v>
       </c>
       <c r="W69">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>3.501500108935892</v>
+        <v>3.299305106316097</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07749823044696005</v>
+        <v>0.07746559156292511</v>
       </c>
       <c r="C70">
-        <v>66.13775447810751</v>
+        <v>64.68532435763925</v>
       </c>
       <c r="D70">
-        <v>175.2337544781075</v>
+        <v>175.4033243576393</v>
       </c>
       <c r="E70">
-        <v>83.196</v>
+        <v>84.81800000000001</v>
       </c>
       <c r="F70">
-        <v>110.296</v>
+        <v>111.918</v>
       </c>
       <c r="G70">
         <v>1.2</v>
@@ -7015,28 +7015,28 @@
         <v>23.326</v>
       </c>
       <c r="M70">
-        <v>7.069973600000001</v>
+        <v>7.173943800000001</v>
       </c>
       <c r="N70">
-        <v>16.2560264</v>
+        <v>16.1520562</v>
       </c>
       <c r="O70">
-        <v>3.576325808</v>
+        <v>3.553452364</v>
       </c>
       <c r="P70">
-        <v>12.679700592</v>
+        <v>12.598603836</v>
       </c>
       <c r="Q70">
-        <v>12.853700592</v>
+        <v>12.772603836</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1359362201467502</v>
+        <v>0.138603134073952</v>
       </c>
       <c r="T70">
-        <v>1.311591830779161</v>
+        <v>1.350398677955736</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.299305106316097</v>
+        <v>3.25148909028253</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07746559156292511</v>
+        <v>0.07743295267889018</v>
       </c>
       <c r="C71">
-        <v>64.68532435763925</v>
+        <v>63.23322273319202</v>
       </c>
       <c r="D71">
-        <v>175.4033243576393</v>
+        <v>175.573222733192</v>
       </c>
       <c r="E71">
-        <v>84.81800000000001</v>
+        <v>86.44</v>
       </c>
       <c r="F71">
-        <v>111.918</v>
+        <v>113.54</v>
       </c>
       <c r="G71">
         <v>1.2</v>
@@ -7097,28 +7097,28 @@
         <v>23.326</v>
       </c>
       <c r="M71">
-        <v>7.173943800000001</v>
+        <v>7.277914000000001</v>
       </c>
       <c r="N71">
-        <v>16.1520562</v>
+        <v>16.048086</v>
       </c>
       <c r="O71">
-        <v>3.553452364</v>
+        <v>3.53057892</v>
       </c>
       <c r="P71">
-        <v>12.598603836</v>
+        <v>12.51750708</v>
       </c>
       <c r="Q71">
-        <v>12.772603836</v>
+        <v>12.69150708</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.138603134073952</v>
+        <v>0.1414478422629672</v>
       </c>
       <c r="T71">
-        <v>1.350398677955736</v>
+        <v>1.391792648277417</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.25148909028253</v>
+        <v>3.205039246135637</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07743295267889018</v>
+        <v>0.07740031379485524</v>
       </c>
       <c r="C72">
-        <v>63.23322273319202</v>
+        <v>61.78145056025059</v>
       </c>
       <c r="D72">
-        <v>175.573222733192</v>
+        <v>175.7434505602506</v>
       </c>
       <c r="E72">
-        <v>86.44</v>
+        <v>88.06200000000001</v>
       </c>
       <c r="F72">
-        <v>113.54</v>
+        <v>115.162</v>
       </c>
       <c r="G72">
         <v>1.2</v>
@@ -7179,28 +7179,28 @@
         <v>23.326</v>
       </c>
       <c r="M72">
-        <v>7.277914000000001</v>
+        <v>7.381884200000001</v>
       </c>
       <c r="N72">
-        <v>16.048086</v>
+        <v>15.9441158</v>
       </c>
       <c r="O72">
-        <v>3.53057892</v>
+        <v>3.507705476</v>
       </c>
       <c r="P72">
-        <v>12.51750708</v>
+        <v>12.436410324</v>
       </c>
       <c r="Q72">
-        <v>12.69150708</v>
+        <v>12.610410324</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1414478422629672</v>
+        <v>0.1444887372236388</v>
       </c>
       <c r="T72">
-        <v>1.391792648277417</v>
+        <v>1.436041375173006</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.205039246135637</v>
+        <v>3.15989784830274</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07740031379485524</v>
+        <v>0.07736767491082031</v>
       </c>
       <c r="C73">
-        <v>61.7814505602506</v>
+        <v>60.33000879800838</v>
       </c>
       <c r="D73">
-        <v>175.7434505602506</v>
+        <v>175.9140087980084</v>
       </c>
       <c r="E73">
-        <v>88.06199999999998</v>
+        <v>89.684</v>
       </c>
       <c r="F73">
-        <v>115.162</v>
+        <v>116.784</v>
       </c>
       <c r="G73">
         <v>1.2</v>
@@ -7261,28 +7261,28 @@
         <v>23.326</v>
       </c>
       <c r="M73">
-        <v>7.3818842</v>
+        <v>7.4858544</v>
       </c>
       <c r="N73">
-        <v>15.9441158</v>
+        <v>15.8401456</v>
       </c>
       <c r="O73">
-        <v>3.507705476</v>
+        <v>3.484832032</v>
       </c>
       <c r="P73">
-        <v>12.436410324</v>
+        <v>12.355313568</v>
       </c>
       <c r="Q73">
-        <v>12.610410324</v>
+        <v>12.529313568</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1444887372236387</v>
+        <v>0.1477468389672153</v>
       </c>
       <c r="T73">
-        <v>1.436041375173005</v>
+        <v>1.48345072541828</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.159897848302741</v>
+        <v>3.116010378187425</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07736767491082031</v>
+        <v>0.07733503602678535</v>
       </c>
       <c r="C74">
-        <v>60.33000879800838</v>
+        <v>58.87889840938651</v>
       </c>
       <c r="D74">
-        <v>175.9140087980084</v>
+        <v>176.0848984093865</v>
       </c>
       <c r="E74">
-        <v>89.684</v>
+        <v>91.30599999999998</v>
       </c>
       <c r="F74">
-        <v>116.784</v>
+        <v>118.406</v>
       </c>
       <c r="G74">
         <v>1.2</v>
@@ -7343,28 +7343,28 @@
         <v>23.326</v>
       </c>
       <c r="M74">
-        <v>7.4858544</v>
+        <v>7.5898246</v>
       </c>
       <c r="N74">
-        <v>15.8401456</v>
+        <v>15.7361754</v>
       </c>
       <c r="O74">
-        <v>3.484832032</v>
+        <v>3.461958588</v>
       </c>
       <c r="P74">
-        <v>12.355313568</v>
+        <v>12.274216812</v>
       </c>
       <c r="Q74">
-        <v>12.529313568</v>
+        <v>12.448216812</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1477468389672153</v>
+        <v>0.1512462815806865</v>
       </c>
       <c r="T74">
-        <v>1.48345072541828</v>
+        <v>1.534371879385426</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.116010378187425</v>
+        <v>3.073325304513625</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07733503602678535</v>
+        <v>0.07730239714275042</v>
       </c>
       <c r="C75">
-        <v>58.87889840938651</v>
+        <v>57.42812036105082</v>
       </c>
       <c r="D75">
-        <v>176.0848984093865</v>
+        <v>176.2561203610508</v>
       </c>
       <c r="E75">
-        <v>91.30599999999998</v>
+        <v>92.928</v>
       </c>
       <c r="F75">
-        <v>118.406</v>
+        <v>120.028</v>
       </c>
       <c r="G75">
         <v>1.2</v>
@@ -7425,28 +7425,28 @@
         <v>23.326</v>
       </c>
       <c r="M75">
-        <v>7.5898246</v>
+        <v>7.6937948</v>
       </c>
       <c r="N75">
-        <v>15.7361754</v>
+        <v>15.6322052</v>
       </c>
       <c r="O75">
-        <v>3.461958588</v>
+        <v>3.439085144</v>
       </c>
       <c r="P75">
-        <v>12.274216812</v>
+        <v>12.193120056</v>
       </c>
       <c r="Q75">
-        <v>12.448216812</v>
+        <v>12.367120056</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1512462815806865</v>
+        <v>0.1550149120875016</v>
       </c>
       <c r="T75">
-        <v>1.534371879385426</v>
+        <v>1.589210045196199</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.073325304513625</v>
+        <v>3.031793881479657</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07730239714275042</v>
+        <v>0.08183275825871547</v>
       </c>
       <c r="C76">
-        <v>57.42812036105082</v>
+        <v>34.84594262857571</v>
       </c>
       <c r="D76">
-        <v>176.2561203610508</v>
+        <v>155.2959426285757</v>
       </c>
       <c r="E76">
-        <v>92.928</v>
+        <v>94.54999999999998</v>
       </c>
       <c r="F76">
-        <v>120.028</v>
+        <v>121.65</v>
       </c>
       <c r="G76">
         <v>1.2</v>
@@ -7507,45 +7507,45 @@
         <v>23.326</v>
       </c>
       <c r="M76">
-        <v>7.6937948</v>
+        <v>8.746634999999999</v>
       </c>
       <c r="N76">
-        <v>15.6322052</v>
+        <v>14.579365</v>
       </c>
       <c r="O76">
-        <v>3.439085144</v>
+        <v>3.2074603</v>
       </c>
       <c r="P76">
-        <v>12.193120056</v>
+        <v>11.3719047</v>
       </c>
       <c r="Q76">
-        <v>12.367120056</v>
+        <v>11.5459047</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1550149120875016</v>
+        <v>0.1590850330348619</v>
       </c>
       <c r="T76">
-        <v>1.589210045196199</v>
+        <v>1.648435264271833</v>
       </c>
       <c r="U76">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V76">
         <v>0.22</v>
       </c>
       <c r="W76">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y76">
-        <v>3.031793881479657</v>
+        <v>2.666854167345499</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08183275825871547</v>
+        <v>0.08186095937468055</v>
       </c>
       <c r="C77">
-        <v>34.84594262857571</v>
+        <v>33.10906830552437</v>
       </c>
       <c r="D77">
-        <v>155.2959426285757</v>
+        <v>155.1810683055244</v>
       </c>
       <c r="E77">
-        <v>94.54999999999998</v>
+        <v>96.172</v>
       </c>
       <c r="F77">
-        <v>121.65</v>
+        <v>123.272</v>
       </c>
       <c r="G77">
         <v>1.2</v>
@@ -7589,28 +7589,28 @@
         <v>23.326</v>
       </c>
       <c r="M77">
-        <v>8.746634999999999</v>
+        <v>8.8632568</v>
       </c>
       <c r="N77">
-        <v>14.579365</v>
+        <v>14.4627432</v>
       </c>
       <c r="O77">
-        <v>3.2074603</v>
+        <v>3.181803504</v>
       </c>
       <c r="P77">
-        <v>11.3719047</v>
+        <v>11.280939696</v>
       </c>
       <c r="Q77">
-        <v>11.5459047</v>
+        <v>11.454939696</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1590850330348619</v>
+        <v>0.1634943307278356</v>
       </c>
       <c r="T77">
-        <v>1.648435264271833</v>
+        <v>1.712595918270438</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.666854167345499</v>
+        <v>2.631763980933059</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08186095937468055</v>
+        <v>0.0818891604906456</v>
       </c>
       <c r="C78">
-        <v>33.10906830552437</v>
+        <v>31.37236380475908</v>
       </c>
       <c r="D78">
-        <v>155.1810683055244</v>
+        <v>155.0663638047591</v>
       </c>
       <c r="E78">
-        <v>96.172</v>
+        <v>97.79399999999998</v>
       </c>
       <c r="F78">
-        <v>123.272</v>
+        <v>124.894</v>
       </c>
       <c r="G78">
         <v>1.2</v>
@@ -7671,28 +7671,28 @@
         <v>23.326</v>
       </c>
       <c r="M78">
-        <v>8.8632568</v>
+        <v>8.979878599999999</v>
       </c>
       <c r="N78">
-        <v>14.4627432</v>
+        <v>14.3461214</v>
       </c>
       <c r="O78">
-        <v>3.181803504</v>
+        <v>3.156146708</v>
       </c>
       <c r="P78">
-        <v>11.280939696</v>
+        <v>11.189974692</v>
       </c>
       <c r="Q78">
-        <v>11.454939696</v>
+        <v>11.363974692</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1634943307278356</v>
+        <v>0.1682870456115026</v>
       </c>
       <c r="T78">
-        <v>1.712595918270438</v>
+        <v>1.782335759573269</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.631763980933059</v>
+        <v>2.597585227933928</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0818891604906456</v>
+        <v>0.08191736160661067</v>
       </c>
       <c r="C79">
-        <v>31.37236380475908</v>
+        <v>29.63582874997741</v>
       </c>
       <c r="D79">
-        <v>155.0663638047591</v>
+        <v>154.9518287499774</v>
       </c>
       <c r="E79">
-        <v>97.79399999999998</v>
+        <v>99.416</v>
       </c>
       <c r="F79">
-        <v>124.894</v>
+        <v>126.516</v>
       </c>
       <c r="G79">
         <v>1.2</v>
@@ -7753,28 +7753,28 @@
         <v>23.326</v>
       </c>
       <c r="M79">
-        <v>8.979878599999999</v>
+        <v>9.0965004</v>
       </c>
       <c r="N79">
-        <v>14.3461214</v>
+        <v>14.2294996</v>
       </c>
       <c r="O79">
-        <v>3.156146708</v>
+        <v>3.130489912</v>
       </c>
       <c r="P79">
-        <v>11.189974692</v>
+        <v>11.099009688</v>
       </c>
       <c r="Q79">
-        <v>11.363974692</v>
+        <v>11.273009688</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1682870456115026</v>
+        <v>0.1735154618482303</v>
       </c>
       <c r="T79">
-        <v>1.782335759573269</v>
+        <v>1.858415586449084</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.597585227933928</v>
+        <v>2.564282853216826</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08191736160661067</v>
+        <v>0.08194556272257572</v>
       </c>
       <c r="C80">
-        <v>29.63582874997741</v>
+        <v>27.89946276598832</v>
       </c>
       <c r="D80">
-        <v>154.9518287499774</v>
+        <v>154.8374627659883</v>
       </c>
       <c r="E80">
-        <v>99.416</v>
+        <v>101.038</v>
       </c>
       <c r="F80">
-        <v>126.516</v>
+        <v>128.138</v>
       </c>
       <c r="G80">
         <v>1.2</v>
@@ -7835,28 +7835,28 @@
         <v>23.326</v>
       </c>
       <c r="M80">
-        <v>9.0965004</v>
+        <v>9.213122200000001</v>
       </c>
       <c r="N80">
-        <v>14.2294996</v>
+        <v>14.1128778</v>
       </c>
       <c r="O80">
-        <v>3.130489912</v>
+        <v>3.104833116</v>
       </c>
       <c r="P80">
-        <v>11.099009688</v>
+        <v>11.008044684</v>
       </c>
       <c r="Q80">
-        <v>11.273009688</v>
+        <v>11.182044684</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1735154618482303</v>
+        <v>0.1792418224884558</v>
       </c>
       <c r="T80">
-        <v>1.858415586449084</v>
+        <v>1.941741111122596</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.564282853216826</v>
+        <v>2.531823576593828</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08194556272257572</v>
+        <v>0.08197376383854078</v>
       </c>
       <c r="C81">
-        <v>27.89946276598832</v>
+        <v>26.16326547870727</v>
       </c>
       <c r="D81">
-        <v>154.8374627659883</v>
+        <v>154.7232654787073</v>
       </c>
       <c r="E81">
-        <v>101.038</v>
+        <v>102.66</v>
       </c>
       <c r="F81">
-        <v>128.138</v>
+        <v>129.76</v>
       </c>
       <c r="G81">
         <v>1.2</v>
@@ -7917,28 +7917,28 @@
         <v>23.326</v>
       </c>
       <c r="M81">
-        <v>9.213122200000001</v>
+        <v>9.329744</v>
       </c>
       <c r="N81">
-        <v>14.1128778</v>
+        <v>13.996256</v>
       </c>
       <c r="O81">
-        <v>3.104833116</v>
+        <v>3.07917632</v>
       </c>
       <c r="P81">
-        <v>11.008044684</v>
+        <v>10.91707968</v>
       </c>
       <c r="Q81">
-        <v>11.182044684</v>
+        <v>11.09107968</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1792418224884558</v>
+        <v>0.1855408191927039</v>
       </c>
       <c r="T81">
-        <v>1.941741111122596</v>
+        <v>2.03339918826346</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.531823576593828</v>
+        <v>2.500175781886406</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08197376383854078</v>
+        <v>0.08446598495450586</v>
       </c>
       <c r="C82">
-        <v>26.16326547870727</v>
+        <v>15.07380469346282</v>
       </c>
       <c r="D82">
-        <v>154.7232654787073</v>
+        <v>145.2558046934628</v>
       </c>
       <c r="E82">
-        <v>102.66</v>
+        <v>104.282</v>
       </c>
       <c r="F82">
-        <v>129.76</v>
+        <v>131.382</v>
       </c>
       <c r="G82">
         <v>1.2</v>
@@ -7999,45 +7999,45 @@
         <v>23.326</v>
       </c>
       <c r="M82">
-        <v>9.329744</v>
+        <v>9.958755600000002</v>
       </c>
       <c r="N82">
-        <v>13.996256</v>
+        <v>13.3672444</v>
       </c>
       <c r="O82">
-        <v>3.07917632</v>
+        <v>2.940793768</v>
       </c>
       <c r="P82">
-        <v>10.91707968</v>
+        <v>10.426450632</v>
       </c>
       <c r="Q82">
-        <v>11.09107968</v>
+        <v>10.600450632</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1855408191927039</v>
+        <v>0.1925028681816097</v>
       </c>
       <c r="T82">
-        <v>2.03339918826346</v>
+        <v>2.13470548405073</v>
       </c>
       <c r="U82">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V82">
         <v>0.22</v>
       </c>
       <c r="W82">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.500175781886406</v>
+        <v>2.342260512950031</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08446598495450586</v>
+        <v>0.08452460607047091</v>
       </c>
       <c r="C83">
-        <v>15.07380469346282</v>
+        <v>13.24304133394011</v>
       </c>
       <c r="D83">
-        <v>145.2558046934628</v>
+        <v>145.0470413339401</v>
       </c>
       <c r="E83">
-        <v>104.282</v>
+        <v>105.904</v>
       </c>
       <c r="F83">
-        <v>131.382</v>
+        <v>133.004</v>
       </c>
       <c r="G83">
         <v>1.2</v>
@@ -8081,28 +8081,28 @@
         <v>23.326</v>
       </c>
       <c r="M83">
-        <v>9.958755600000002</v>
+        <v>10.0817032</v>
       </c>
       <c r="N83">
-        <v>13.3672444</v>
+        <v>13.2442968</v>
       </c>
       <c r="O83">
-        <v>2.940793768</v>
+        <v>2.913745296</v>
       </c>
       <c r="P83">
-        <v>10.426450632</v>
+        <v>10.330551504</v>
       </c>
       <c r="Q83">
-        <v>10.600450632</v>
+        <v>10.504551504</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1925028681816097</v>
+        <v>0.2002384781692828</v>
       </c>
       <c r="T83">
-        <v>2.13470548405073</v>
+        <v>2.247268034925474</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.342260512950031</v>
+        <v>2.31369636035308</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08452460607047091</v>
+        <v>0.08458322718643597</v>
       </c>
       <c r="C84">
-        <v>13.24304133394011</v>
+        <v>11.4128771875572</v>
       </c>
       <c r="D84">
-        <v>145.0470413339401</v>
+        <v>144.8388771875572</v>
       </c>
       <c r="E84">
-        <v>105.904</v>
+        <v>107.526</v>
       </c>
       <c r="F84">
-        <v>133.004</v>
+        <v>134.626</v>
       </c>
       <c r="G84">
         <v>1.2</v>
@@ -8163,28 +8163,28 @@
         <v>23.326</v>
       </c>
       <c r="M84">
-        <v>10.0817032</v>
+        <v>10.2046508</v>
       </c>
       <c r="N84">
-        <v>13.2442968</v>
+        <v>13.1213492</v>
       </c>
       <c r="O84">
-        <v>2.913745296</v>
+        <v>2.886696824</v>
       </c>
       <c r="P84">
-        <v>10.330551504</v>
+        <v>10.234652376</v>
       </c>
       <c r="Q84">
-        <v>10.504551504</v>
+        <v>10.408652376</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2002384781692828</v>
+        <v>0.2088841599202116</v>
       </c>
       <c r="T84">
-        <v>2.247268034925474</v>
+        <v>2.373073238844307</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.31369636035308</v>
+        <v>2.285820500589789</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08458322718643597</v>
+        <v>0.08464184830240104</v>
       </c>
       <c r="C85">
-        <v>11.4128771875572</v>
+        <v>9.583309678130576</v>
       </c>
       <c r="D85">
-        <v>144.8388771875572</v>
+        <v>144.6313096781306</v>
       </c>
       <c r="E85">
-        <v>107.526</v>
+        <v>109.148</v>
       </c>
       <c r="F85">
-        <v>134.626</v>
+        <v>136.248</v>
       </c>
       <c r="G85">
         <v>1.2</v>
@@ -8245,28 +8245,28 @@
         <v>23.326</v>
       </c>
       <c r="M85">
-        <v>10.2046508</v>
+        <v>10.3275984</v>
       </c>
       <c r="N85">
-        <v>13.1213492</v>
+        <v>12.9984016</v>
       </c>
       <c r="O85">
-        <v>2.886696824</v>
+        <v>2.859648352</v>
       </c>
       <c r="P85">
-        <v>10.234652376</v>
+        <v>10.138753248</v>
       </c>
       <c r="Q85">
-        <v>10.408652376</v>
+        <v>10.312753248</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2088841599202116</v>
+        <v>0.2186105518900065</v>
       </c>
       <c r="T85">
-        <v>2.373073238844307</v>
+        <v>2.514604093252993</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.285820500589789</v>
+        <v>2.258608351773245</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08464184830240104</v>
+        <v>0.08470046941836609</v>
       </c>
       <c r="C86">
-        <v>9.583309678130576</v>
+        <v>7.754336244223168</v>
       </c>
       <c r="D86">
-        <v>144.6313096781306</v>
+        <v>144.4243362442232</v>
       </c>
       <c r="E86">
-        <v>109.148</v>
+        <v>110.77</v>
       </c>
       <c r="F86">
-        <v>136.248</v>
+        <v>137.87</v>
       </c>
       <c r="G86">
         <v>1.2</v>
@@ -8327,28 +8327,28 @@
         <v>23.326</v>
       </c>
       <c r="M86">
-        <v>10.3275984</v>
+        <v>10.450546</v>
       </c>
       <c r="N86">
-        <v>12.9984016</v>
+        <v>12.875454</v>
       </c>
       <c r="O86">
-        <v>2.859648352</v>
+        <v>2.832599880000001</v>
       </c>
       <c r="P86">
-        <v>10.138753248</v>
+        <v>10.04285412</v>
       </c>
       <c r="Q86">
-        <v>10.312753248</v>
+        <v>10.21685412</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2186105518900064</v>
+        <v>0.2296337961224406</v>
       </c>
       <c r="T86">
-        <v>2.514604093252991</v>
+        <v>2.675005728249502</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.258608351773245</v>
+        <v>2.232036488811207</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08470046941836609</v>
+        <v>0.08475909053433114</v>
       </c>
       <c r="C87">
-        <v>7.754336244223168</v>
+        <v>5.925954339038981</v>
       </c>
       <c r="D87">
-        <v>144.4243362442232</v>
+        <v>144.217954339039</v>
       </c>
       <c r="E87">
-        <v>110.77</v>
+        <v>112.392</v>
       </c>
       <c r="F87">
-        <v>137.87</v>
+        <v>139.492</v>
       </c>
       <c r="G87">
         <v>1.2</v>
@@ -8409,28 +8409,28 @@
         <v>23.326</v>
       </c>
       <c r="M87">
-        <v>10.450546</v>
+        <v>10.5734936</v>
       </c>
       <c r="N87">
-        <v>12.875454</v>
+        <v>12.7525064</v>
       </c>
       <c r="O87">
-        <v>2.832599880000001</v>
+        <v>2.805551408</v>
       </c>
       <c r="P87">
-        <v>10.04285412</v>
+        <v>9.946954992</v>
       </c>
       <c r="Q87">
-        <v>10.21685412</v>
+        <v>10.120954992</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2296337961224406</v>
+        <v>0.2422317895309367</v>
       </c>
       <c r="T87">
-        <v>2.675005728249502</v>
+        <v>2.858321882531229</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.232036488811207</v>
+        <v>2.206082576150611</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08475909053433114</v>
+        <v>0.08481771165029621</v>
       </c>
       <c r="C88">
-        <v>5.925954339038981</v>
+        <v>4.098161430318783</v>
       </c>
       <c r="D88">
-        <v>144.217954339039</v>
+        <v>144.0121614303188</v>
       </c>
       <c r="E88">
-        <v>112.392</v>
+        <v>114.014</v>
       </c>
       <c r="F88">
-        <v>139.492</v>
+        <v>141.114</v>
       </c>
       <c r="G88">
         <v>1.2</v>
@@ -8491,28 +8491,28 @@
         <v>23.326</v>
       </c>
       <c r="M88">
-        <v>10.5734936</v>
+        <v>10.6964412</v>
       </c>
       <c r="N88">
-        <v>12.7525064</v>
+        <v>12.6295588</v>
       </c>
       <c r="O88">
-        <v>2.805551408</v>
+        <v>2.778502936</v>
       </c>
       <c r="P88">
-        <v>9.946954992</v>
+        <v>9.851055864000001</v>
       </c>
       <c r="Q88">
-        <v>10.120954992</v>
+        <v>10.025055864</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2422317895309367</v>
+        <v>0.2567679357715092</v>
       </c>
       <c r="T88">
-        <v>2.858321882531229</v>
+        <v>3.069840522087067</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.206082576150611</v>
+        <v>2.180725305160375</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08481771165029621</v>
+        <v>0.08487633276626128</v>
       </c>
       <c r="C89">
-        <v>4.098161430318783</v>
+        <v>2.270955000236398</v>
       </c>
       <c r="D89">
-        <v>144.0121614303188</v>
+        <v>143.8069550002364</v>
       </c>
       <c r="E89">
-        <v>114.014</v>
+        <v>115.636</v>
       </c>
       <c r="F89">
-        <v>141.114</v>
+        <v>142.736</v>
       </c>
       <c r="G89">
         <v>1.2</v>
@@ -8573,28 +8573,28 @@
         <v>23.326</v>
       </c>
       <c r="M89">
-        <v>10.6964412</v>
+        <v>10.8193888</v>
       </c>
       <c r="N89">
-        <v>12.6295588</v>
+        <v>12.5066112</v>
       </c>
       <c r="O89">
-        <v>2.778502936</v>
+        <v>2.751454464</v>
       </c>
       <c r="P89">
-        <v>9.851055864000001</v>
+        <v>9.755156736</v>
       </c>
       <c r="Q89">
-        <v>10.025055864</v>
+        <v>9.929156735999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2567679357715092</v>
+        <v>0.2737267730521772</v>
       </c>
       <c r="T89">
-        <v>3.069840522087067</v>
+        <v>3.316612268235546</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.180725305160375</v>
+        <v>2.155944335783552</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08487633276626128</v>
+        <v>0.08493495388222634</v>
       </c>
       <c r="C90">
-        <v>2.270955000236398</v>
+        <v>0.4443325452961346</v>
       </c>
       <c r="D90">
-        <v>143.8069550002364</v>
+        <v>143.6023325452962</v>
       </c>
       <c r="E90">
-        <v>115.636</v>
+        <v>117.258</v>
       </c>
       <c r="F90">
-        <v>142.736</v>
+        <v>144.358</v>
       </c>
       <c r="G90">
         <v>1.2</v>
@@ -8655,28 +8655,28 @@
         <v>23.326</v>
       </c>
       <c r="M90">
-        <v>10.8193888</v>
+        <v>10.9423364</v>
       </c>
       <c r="N90">
-        <v>12.5066112</v>
+        <v>12.3836636</v>
       </c>
       <c r="O90">
-        <v>2.751454464</v>
+        <v>2.724405992</v>
       </c>
       <c r="P90">
-        <v>9.755156736</v>
+        <v>9.659257607999999</v>
       </c>
       <c r="Q90">
-        <v>9.929156735999999</v>
+        <v>9.833257607999998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2737267730521772</v>
+        <v>0.2937690352929667</v>
       </c>
       <c r="T90">
-        <v>3.316612268235546</v>
+        <v>3.608251604592838</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.155944335783552</v>
+        <v>2.131720242123062</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08493495388222634</v>
+        <v>0.08499357499819141</v>
       </c>
       <c r="C91">
-        <v>0.4443325452961346</v>
+        <v>-1.381708423769027</v>
       </c>
       <c r="D91">
-        <v>143.6023325452962</v>
+        <v>143.398291576231</v>
       </c>
       <c r="E91">
-        <v>117.258</v>
+        <v>118.88</v>
       </c>
       <c r="F91">
-        <v>144.358</v>
+        <v>145.98</v>
       </c>
       <c r="G91">
         <v>1.2</v>
@@ -8737,28 +8737,28 @@
         <v>23.326</v>
       </c>
       <c r="M91">
-        <v>10.9423364</v>
+        <v>11.065284</v>
       </c>
       <c r="N91">
-        <v>12.3836636</v>
+        <v>12.260716</v>
       </c>
       <c r="O91">
-        <v>2.724405992</v>
+        <v>2.69735752</v>
       </c>
       <c r="P91">
-        <v>9.659257607999999</v>
+        <v>9.56335848</v>
       </c>
       <c r="Q91">
-        <v>9.833257607999998</v>
+        <v>9.737358479999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2937690352929667</v>
+        <v>0.317819749981914</v>
       </c>
       <c r="T91">
-        <v>3.608251604592838</v>
+        <v>3.958218808221589</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.131720242123062</v>
+        <v>2.108034461655028</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08499357499819141</v>
+        <v>0.08505219611415646</v>
       </c>
       <c r="C92">
-        <v>-1.381708423769027</v>
+        <v>-3.20717038209861</v>
       </c>
       <c r="D92">
-        <v>143.398291576231</v>
+        <v>143.1948296179014</v>
       </c>
       <c r="E92">
-        <v>118.88</v>
+        <v>120.502</v>
       </c>
       <c r="F92">
-        <v>145.98</v>
+        <v>147.602</v>
       </c>
       <c r="G92">
         <v>1.2</v>
@@ -8819,28 +8819,28 @@
         <v>23.326</v>
       </c>
       <c r="M92">
-        <v>11.065284</v>
+        <v>11.1882316</v>
       </c>
       <c r="N92">
-        <v>12.260716</v>
+        <v>12.1377684</v>
       </c>
       <c r="O92">
-        <v>2.69735752</v>
+        <v>2.670309048</v>
       </c>
       <c r="P92">
-        <v>9.56335848</v>
+        <v>9.467459351999999</v>
       </c>
       <c r="Q92">
-        <v>9.737358479999999</v>
+        <v>9.641459351999998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.317819749981914</v>
+        <v>0.3472150679350718</v>
       </c>
       <c r="T92">
-        <v>3.958218808221589</v>
+        <v>4.385956501545619</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.108034461655028</v>
+        <v>2.084869247790687</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08505219611415646</v>
+        <v>0.08511081723012152</v>
       </c>
       <c r="C93">
-        <v>-3.20717038209861</v>
+        <v>-5.032055790804407</v>
       </c>
       <c r="D93">
-        <v>143.1948296179014</v>
+        <v>142.9919442091956</v>
       </c>
       <c r="E93">
-        <v>120.502</v>
+        <v>122.124</v>
       </c>
       <c r="F93">
-        <v>147.602</v>
+        <v>149.224</v>
       </c>
       <c r="G93">
         <v>1.2</v>
@@ -8901,28 +8901,28 @@
         <v>23.326</v>
       </c>
       <c r="M93">
-        <v>11.1882316</v>
+        <v>11.3111792</v>
       </c>
       <c r="N93">
-        <v>12.1377684</v>
+        <v>12.0148208</v>
       </c>
       <c r="O93">
-        <v>2.670309048</v>
+        <v>2.643260576</v>
       </c>
       <c r="P93">
-        <v>9.467459351999999</v>
+        <v>9.371560224</v>
       </c>
       <c r="Q93">
-        <v>9.641459351999998</v>
+        <v>9.545560223999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3472150679350718</v>
+        <v>0.3839592153765191</v>
       </c>
       <c r="T93">
-        <v>4.385956501545619</v>
+        <v>4.920628618200656</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.084869247790687</v>
+        <v>2.062207625532093</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08511081723012152</v>
+        <v>0.08516943834608659</v>
       </c>
       <c r="C94">
-        <v>-5.032055790804407</v>
+        <v>-6.856367097069921</v>
       </c>
       <c r="D94">
-        <v>142.9919442091956</v>
+        <v>142.7896329029301</v>
       </c>
       <c r="E94">
-        <v>122.124</v>
+        <v>123.746</v>
       </c>
       <c r="F94">
-        <v>149.224</v>
+        <v>150.846</v>
       </c>
       <c r="G94">
         <v>1.2</v>
@@ -8983,28 +8983,28 @@
         <v>23.326</v>
       </c>
       <c r="M94">
-        <v>11.3111792</v>
+        <v>11.4341268</v>
       </c>
       <c r="N94">
-        <v>12.0148208</v>
+        <v>11.8918732</v>
       </c>
       <c r="O94">
-        <v>2.643260576</v>
+        <v>2.616212104</v>
       </c>
       <c r="P94">
-        <v>9.371560224</v>
+        <v>9.275661096</v>
       </c>
       <c r="Q94">
-        <v>9.545560223999999</v>
+        <v>9.449661096</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3839592153765191</v>
+        <v>0.4312016906583799</v>
       </c>
       <c r="T94">
-        <v>4.920628618200656</v>
+        <v>5.608064196757131</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.062207625532093</v>
+        <v>2.040033349988737</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08516943834608659</v>
+        <v>0.08522805946205164</v>
       </c>
       <c r="C95">
-        <v>-6.856367097069921</v>
+        <v>-8.680106734248568</v>
       </c>
       <c r="D95">
-        <v>142.7896329029301</v>
+        <v>142.5878932657514</v>
       </c>
       <c r="E95">
-        <v>123.746</v>
+        <v>125.368</v>
       </c>
       <c r="F95">
-        <v>150.846</v>
+        <v>152.468</v>
       </c>
       <c r="G95">
         <v>1.2</v>
@@ -9065,28 +9065,28 @@
         <v>23.326</v>
       </c>
       <c r="M95">
-        <v>11.4341268</v>
+        <v>11.5570744</v>
       </c>
       <c r="N95">
-        <v>11.8918732</v>
+        <v>11.7689256</v>
       </c>
       <c r="O95">
-        <v>2.616212104</v>
+        <v>2.589163632</v>
       </c>
       <c r="P95">
-        <v>9.275661096</v>
+        <v>9.179761968000001</v>
       </c>
       <c r="Q95">
-        <v>9.449661096</v>
+        <v>9.353761968000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4312016906583799</v>
+        <v>0.494191657700861</v>
       </c>
       <c r="T95">
-        <v>5.608064196757131</v>
+        <v>6.524644968165767</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.040033349988737</v>
+        <v>2.018330867542049</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08522805946205164</v>
+        <v>0.09580888057801669</v>
       </c>
       <c r="C96">
-        <v>-8.680106734248568</v>
+        <v>-39.2751942857242</v>
       </c>
       <c r="D96">
-        <v>142.5878932657514</v>
+        <v>113.6148057142758</v>
       </c>
       <c r="E96">
-        <v>125.368</v>
+        <v>126.99</v>
       </c>
       <c r="F96">
-        <v>152.468</v>
+        <v>154.09</v>
       </c>
       <c r="G96">
         <v>1.2</v>
@@ -9147,45 +9147,45 @@
         <v>23.326</v>
       </c>
       <c r="M96">
-        <v>11.5570744</v>
+        <v>13.8681</v>
       </c>
       <c r="N96">
-        <v>11.7689256</v>
+        <v>9.4579</v>
       </c>
       <c r="O96">
-        <v>2.589163632</v>
+        <v>2.080738</v>
       </c>
       <c r="P96">
-        <v>9.179761968000001</v>
+        <v>7.377162</v>
       </c>
       <c r="Q96">
-        <v>9.353761968000001</v>
+        <v>7.551162000000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.494191657700861</v>
+        <v>0.5823776115603346</v>
       </c>
       <c r="T96">
-        <v>6.524644968165767</v>
+        <v>7.807858048137858</v>
       </c>
       <c r="U96">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V96">
         <v>0.22</v>
       </c>
       <c r="W96">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y96">
-        <v>2.018330867542049</v>
+        <v>1.681989602036328</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09580888057801669</v>
+        <v>0.09597826169398176</v>
       </c>
       <c r="C97">
-        <v>-39.2751942857242</v>
+        <v>-41.26556262202358</v>
       </c>
       <c r="D97">
-        <v>113.6148057142758</v>
+        <v>113.2464373779764</v>
       </c>
       <c r="E97">
-        <v>126.99</v>
+        <v>128.612</v>
       </c>
       <c r="F97">
-        <v>154.09</v>
+        <v>155.712</v>
       </c>
       <c r="G97">
         <v>1.2</v>
@@ -9229,28 +9229,28 @@
         <v>23.326</v>
       </c>
       <c r="M97">
-        <v>13.8681</v>
+        <v>14.01408</v>
       </c>
       <c r="N97">
-        <v>9.4579</v>
+        <v>9.311920000000002</v>
       </c>
       <c r="O97">
-        <v>2.080738</v>
+        <v>2.048622400000001</v>
       </c>
       <c r="P97">
-        <v>7.377162</v>
+        <v>7.263297600000001</v>
       </c>
       <c r="Q97">
-        <v>7.551162000000001</v>
+        <v>7.437297600000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5823776115603346</v>
+        <v>0.7146565423495451</v>
       </c>
       <c r="T97">
-        <v>7.807858048137858</v>
+        <v>9.732677668095993</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.681989602036328</v>
+        <v>1.664468877015116</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09597826169398176</v>
+        <v>0.09614764280994682</v>
       </c>
       <c r="C98">
-        <v>-41.26556262202358</v>
+        <v>-43.25354998881024</v>
       </c>
       <c r="D98">
-        <v>113.2464373779764</v>
+        <v>112.8804500111897</v>
       </c>
       <c r="E98">
-        <v>128.612</v>
+        <v>130.234</v>
       </c>
       <c r="F98">
-        <v>155.712</v>
+        <v>157.334</v>
       </c>
       <c r="G98">
         <v>1.2</v>
@@ -9311,28 +9311,28 @@
         <v>23.326</v>
       </c>
       <c r="M98">
-        <v>14.01408</v>
+        <v>14.16006</v>
       </c>
       <c r="N98">
-        <v>9.311920000000002</v>
+        <v>9.165940000000003</v>
       </c>
       <c r="O98">
-        <v>2.048622400000001</v>
+        <v>2.016506800000001</v>
       </c>
       <c r="P98">
-        <v>7.263297600000001</v>
+        <v>7.149433200000002</v>
       </c>
       <c r="Q98">
-        <v>7.437297600000002</v>
+        <v>7.323433200000003</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7146565423495433</v>
+        <v>0.9351214269982265</v>
       </c>
       <c r="T98">
-        <v>9.732677668095969</v>
+        <v>12.94071036802618</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.664468877015116</v>
+        <v>1.647309404056198</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09614764280994682</v>
+        <v>0.09631702392591188</v>
       </c>
       <c r="C99">
-        <v>-43.25354998881024</v>
+        <v>-45.23917939601725</v>
       </c>
       <c r="D99">
-        <v>112.8804500111897</v>
+        <v>112.5168206039827</v>
       </c>
       <c r="E99">
-        <v>130.234</v>
+        <v>131.856</v>
       </c>
       <c r="F99">
-        <v>157.334</v>
+        <v>158.956</v>
       </c>
       <c r="G99">
         <v>1.2</v>
@@ -9393,28 +9393,28 @@
         <v>23.326</v>
       </c>
       <c r="M99">
-        <v>14.16006</v>
+        <v>14.30604</v>
       </c>
       <c r="N99">
-        <v>9.165940000000003</v>
+        <v>9.019960000000003</v>
       </c>
       <c r="O99">
-        <v>2.016506800000001</v>
+        <v>1.984391200000001</v>
       </c>
       <c r="P99">
-        <v>7.149433200000002</v>
+        <v>7.035568800000002</v>
       </c>
       <c r="Q99">
-        <v>7.323433200000003</v>
+        <v>7.209568800000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9351214269982265</v>
+        <v>1.376051196295593</v>
       </c>
       <c r="T99">
-        <v>12.94071036802618</v>
+        <v>19.35677576788661</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.647309404056198</v>
+        <v>1.630500124422971</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09631702392591188</v>
+        <v>0.09648640504187694</v>
       </c>
       <c r="C100">
-        <v>-45.23917939601725</v>
+        <v>-47.22247355803592</v>
       </c>
       <c r="D100">
-        <v>112.5168206039827</v>
+        <v>112.1555264419641</v>
       </c>
       <c r="E100">
-        <v>131.856</v>
+        <v>133.478</v>
       </c>
       <c r="F100">
-        <v>158.956</v>
+        <v>160.578</v>
       </c>
       <c r="G100">
         <v>1.2</v>
@@ -9475,28 +9475,28 @@
         <v>23.326</v>
       </c>
       <c r="M100">
-        <v>14.30604</v>
+        <v>14.45202</v>
       </c>
       <c r="N100">
-        <v>9.019960000000003</v>
+        <v>8.873980000000003</v>
       </c>
       <c r="O100">
-        <v>1.984391200000001</v>
+        <v>1.952275600000001</v>
       </c>
       <c r="P100">
-        <v>7.035568800000002</v>
+        <v>6.921704400000002</v>
       </c>
       <c r="Q100">
-        <v>7.209568800000002</v>
+        <v>7.095704400000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.376051196295593</v>
+        <v>2.698840504187692</v>
       </c>
       <c r="T100">
-        <v>19.35677576788661</v>
+        <v>38.60497196746788</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.630500124422971</v>
+        <v>1.614030426196477</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09648640504187694</v>
-      </c>
-      <c r="C101">
-        <v>-47.22247355803592</v>
-      </c>
-      <c r="D101">
-        <v>112.1555264419641</v>
-      </c>
-      <c r="E101">
-        <v>133.478</v>
-      </c>
-      <c r="F101">
-        <v>160.578</v>
-      </c>
-      <c r="G101">
-        <v>1.2</v>
-      </c>
-      <c r="H101">
-        <v>135.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>23.5</v>
-      </c>
-      <c r="K101">
-        <v>0.174</v>
-      </c>
-      <c r="L101">
-        <v>23.326</v>
-      </c>
-      <c r="M101">
-        <v>14.45202</v>
-      </c>
-      <c r="N101">
-        <v>8.873980000000003</v>
-      </c>
-      <c r="O101">
-        <v>1.952275600000001</v>
-      </c>
-      <c r="P101">
-        <v>6.921704400000002</v>
-      </c>
-      <c r="Q101">
-        <v>7.095704400000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.698840504187692</v>
-      </c>
-      <c r="T101">
-        <v>38.60497196746788</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.22</v>
-      </c>
-      <c r="W101">
-        <v>0.0702</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.614030426196477</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
